--- a/output/china_yearbook_provincial.xlsx
+++ b/output/china_yearbook_provincial.xlsx
@@ -9,11 +9,16 @@
   <sheets>
     <sheet name="説明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="GDP 地区生产总值" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="小売 社会消费品零售总额" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="貿易 货物进出口" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="不動産 开发完成投资" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="全国 商品房销售面积" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="全国 商品房销售额" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="一人当たりGDP 人均" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="小売 社会消费品零售总额" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="貿易 货物进出口" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="不動産 开发完成投资" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="全国 商品房销售面积" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="全国 商品房销售额" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="対中投資FDI(全国推移)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="対外投資ODI(全国推移)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="対中投資FDI(国別)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="対外投資ODI(国別)" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +31,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +46,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -77,6 +86,8 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,6 +509,2535 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>対外投資ODI(全国推移)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>単位: 億米ドル / 100 mil. USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年 / Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>122.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>211.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>265.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>559.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>565.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>688.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>746.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>1078.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1231.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1456.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>1961.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>1582.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1430.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>1369.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1537.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1788.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2006-2021年为全行业对外直接投资数据。</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C129"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>対中投資FDI(国別)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>単位: 万米ドル / 10,000 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>国・地域 / Country</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>18095721</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>18913241</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>亚洲</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>15364464</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>16356555</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>孟加拉国</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>文莱</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>658</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>缅甸</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>3369</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>5217</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>塞浦路斯</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>460</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>15075</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>中国香港</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>13175642</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>13724149</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>632</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>2434</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>伊拉克</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>以色列</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>4255</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>8101</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>391325</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>460508</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>约旦</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>344</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>科威特</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>192</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>老挝</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>黎巴嫩</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>中国澳门</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>218948</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>124291</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>马来西亚</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>5770</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>112697</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>蒙古</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>506</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>巴基斯坦</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>菲律宾</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>941</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>卡塔尔</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>沙特阿拉伯</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>7300</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>1033164</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>1059894</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>韩国</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>404469</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>659872</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>斯里兰卡</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>10741</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>6809</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>土耳其</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>5243</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>阿联酋</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>2229</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>96424</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>也门</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>603</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>中国台湾</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>93990</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>66110</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>东帝汶</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>550</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>土库曼斯坦</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>乌兹别克斯坦</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>483</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>非洲</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>108884</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>33765</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>喀麦隆</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>501</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>刚果(布)</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>埃及</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>加纳</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>马里</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>毛里塔尼亚</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>396</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>毛里求斯</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>89774</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>6594</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>摩洛哥</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>纳米比亚</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>853</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>塞舌尔</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>16868</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>14572</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>南非</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>384</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>10319</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>坦桑尼亚</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>乌干达</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>赞比亚</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>非洲其他国家(地区)</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>711570</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>1197604</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>比利时</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>11519</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>18353</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>丹麦</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>21713</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>42596</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>119971</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>159819</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>168019</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>256643</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>法国</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>71013</v>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>75650</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>爱尔兰</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>19341</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>17095</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>意大利</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>17756</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>14847</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>卢森堡</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>31091</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>16059</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>110544</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>449402</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>希腊</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>葡萄牙</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>720</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>西班牙</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>8936</v>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>12335</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>安道尔</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>奥地利</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>9368</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>15530</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>保加利亚</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>芬兰</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>6333</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>匈牙利</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>720</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>冰岛</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>列支敦士登</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>1077</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>摩纳哥</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>260</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>挪威</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="n">
+        <v>5559</v>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>6623</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>波兰</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="n">
+        <v>444</v>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>罗马尼亚</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>202</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>瑞典</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>30141</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>54233</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>瑞士</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>73144</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>39152</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>爱沙尼亚</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>10111</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>立陶宛</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>阿塞拜疆</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>白俄罗斯</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>俄罗斯联邦</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>754</v>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>3895</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>斯洛文尼亚</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>克罗地亚</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>捷克</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="n">
+        <v>408</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>斯洛伐克</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>塞尔维亚</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>欧洲其他国家(地区)</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="n">
+        <v>1255</v>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>拉丁美洲</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="n">
+        <v>783725</v>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>916876</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>安提瓜和巴布达</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="7" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>阿根廷</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>巴巴多斯</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="n">
+        <v>1353</v>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>伯利兹</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="n">
+        <v>2538</v>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="n">
+        <v>1553</v>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>开曼群岛</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="n">
+        <v>246157</v>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>241631</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>智利</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="n">
+        <v>427</v>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>古巴</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>多米尼加共和国</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>危地马拉</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>圭亚那</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>墨西哥</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="n">
+        <v>373</v>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>巴拿马</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>秘鲁</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>特立尼达和多巴哥</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>特克斯和凯科斯群岛</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>乌拉圭</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>委内瑞拉</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>英属维尔京群岛</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="n">
+        <v>528097</v>
+      </c>
+      <c r="C114" s="7" t="n">
+        <v>663493</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>圣其茨和尼维斯</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="n">
+        <v>725</v>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>拉丁美洲其他国家(地区)</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="n">
+        <v>2137</v>
+      </c>
+      <c r="C116" s="7" t="n">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>北美洲</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="n">
+        <v>279199</v>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>287839</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="n">
+        <v>20269</v>
+      </c>
+      <c r="C118" s="7" t="n">
+        <v>16571</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="n">
+        <v>246746</v>
+      </c>
+      <c r="C119" s="7" t="n">
+        <v>221457</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>百慕大</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="n">
+        <v>12184</v>
+      </c>
+      <c r="C120" s="7" t="n">
+        <v>49811</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>大洋洲</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="n">
+        <v>98004</v>
+      </c>
+      <c r="C121" s="7" t="n">
+        <v>120516</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>澳大利亚</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="n">
+        <v>29953</v>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>40211</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>库克群岛</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="7" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>新西兰</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="n">
+        <v>1782</v>
+      </c>
+      <c r="C124" s="7" t="n">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>萨摩亚</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="n">
+        <v>62144</v>
+      </c>
+      <c r="C125" s="7" t="n">
+        <v>74734</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>马绍尔群岛</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="n">
+        <v>2705</v>
+      </c>
+      <c r="C126" s="7" t="n">
+        <v>4271</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>大洋洲其他国家(地区)</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="n">
+        <v>1420</v>
+      </c>
+      <c r="C127" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="n">
+        <v>2485</v>
+      </c>
+      <c r="C128" s="7" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>注：2021年各国家(地区)数据不包含银行、证券、保险领域数据。</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="n">
+        <v/>
+      </c>
+      <c r="C129" s="7" t="n">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>対外投資ODI(国別)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>単位: 万米ドル / 10,000 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>国・地域 / Country</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2020流量</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2021流量</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2021末存量</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>15371026</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>17881932</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>278514971</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>亚洲</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>11234365</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>12810205</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>177201520</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>中国香港</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>8914586</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>10119088</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>154965764</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>20519</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>27946</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>351889</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>印度尼西亚</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>219835</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>437251</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2008048</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>48683</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>76214</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>488287</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>中国澳门</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>82684</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>88192</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1123624</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>新加坡</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>592335</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>840504</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>6720228</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>韩国</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>13914</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>47804</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>660150</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>泰国</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>188288</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>148601</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>991721</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>越南</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>187575</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>220762</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>1085211</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>非洲</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>422560</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>498664</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>4418621</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>阿尔及利亚</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>1864</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>18471</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>171602</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>苏丹</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>283</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>9429</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>111552</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>几内亚</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>-29512</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>48717</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>95933</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>马达加斯加</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>13598</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>-962</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>32287</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>尼日利亚</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>30894</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>20167</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>269579</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>南非</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>40043</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>36359</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>529417</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>欧洲</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>1269565</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>1087480</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>13479438</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>92222</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>190355</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>1900531</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>德国</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>137560</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>271113</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>1669749</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>法国</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>14779</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>-15167</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>486390</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>俄罗斯联邦</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>57032</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>-107230</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>1064411</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>拉丁美洲</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>1665651</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>2615851</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>69374017</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>巴西</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>31264</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>14645</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>300771</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>开曼群岛</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>856222</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>1075356</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>22952507</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>墨西哥</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>26456</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>23183</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>130216</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>英属维尔京群岛</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>697562</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>1397101</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>44747734</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>北美洲</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>634312</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>658090</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>10022580</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>加拿大</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>21002</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>93017</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>1379315</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>601867</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>558435</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>7717236</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>大洋洲</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>144573</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>211642</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>4018796</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>澳大利亚</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>119859</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>192254</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>3443047</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>新西兰</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>22461</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>312871</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -947,6 +3487,354 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>一人当たりGDP 人均</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>地区/地域</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>人均地区生产总值(元)
+2022 値</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>190313</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>119235</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>56995</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>73675</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>内モンゴル</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>96474</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>遼寧</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>68775</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>55347</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>黒龍江</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>51096</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>179907</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>江蘇</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>144390</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>118496</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>73603</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>126829</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>70923</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>山東</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>86003</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>62106</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>92059</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>73598</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>広東</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>101905</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>広西</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>52164</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>66602</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>重慶</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>90663</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>67777</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>貴州</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>52321</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>雲南</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>61716</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>チベット</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>58438</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>陝西</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>82864</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>甘粛</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>44968</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>60724</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>寧夏</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>69781</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>68552</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1613,7 +4501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2177,7 +5065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2447,244 +5335,6 @@
       </c>
       <c r="B35" s="4" t="n">
         <v>1158.8633</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>全国 商品房销售面积</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>地区/地域</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-1998 値</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2000 値</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2005 値</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2006 値</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2007 値</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2008 値</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2009 値</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2010 値</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2011 値</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2012 値</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2013 値</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2014 値</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2015 値</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2016 値</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2017 値</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2018 値</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2019 値</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2020 値</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2021 値</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2022 値</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>全国</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>12185.3</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>18637.128</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>55486.2247</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>61857.0733</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>77354.71799999999</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>65969.83</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>94755</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>104482.7556101567</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>108662.065834563</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>110074.6726904123</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>128347.0683570207</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>118335.9970251731</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>125475.7646102896</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>152578.5297661122</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>163427.0326061051</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>164947.3403961267</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>164531.4239690406</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>168560.4128347682</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>171414.5985785524</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>129766.3947</v>
       </c>
     </row>
   </sheetData>
@@ -2727,7 +5377,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全国 商品房销售额</t>
+          <t>全国 商品房销售面积</t>
         </is>
       </c>
     </row>
@@ -2739,6 +5389,244 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>商品房销售面积
+1998 値</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2000 値</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2005 値</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2006 値</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2007 値</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2008 値</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2009 値</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2010 値</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2011 値</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2012 値</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2013 値</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2014 値</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2015 値</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2016 値</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2017 値</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2018 値</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2019 値</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2020 値</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2021 値</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售面积
+2022 値</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>12185.3</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>18637.128</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>55486.2247</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>61857.0733</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>77354.71799999999</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>65969.83</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>94755</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>104482.7556101567</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>108662.065834563</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>110074.6726904123</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>128347.0683570207</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>118335.9970251731</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>125475.7646102896</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>152578.5297661122</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>163427.0326061051</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>164947.3403961267</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>164531.4239690406</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>168560.4128347682</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>171414.5985785524</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>129766.3947</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>全国 商品房销售额</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>地区/地域</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>商品房销售额
 1998 値</t>
         </is>
@@ -2923,6 +5811,460 @@
       </c>
       <c r="U4" s="4" t="n">
         <v>129655.5699</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>対中投資FDI(全国推移)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>単位: 億米ドル / 100 mil. USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年 / Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1979-1982</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>43.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>110.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>275.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>337.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>375.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>417.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>452.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>454.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>403.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>407.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>468.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>527.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>606.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>724.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>727.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>835.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>1083.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>940.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>1147.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>1239.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>1210.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>1239.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>1355.8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>1337.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>1363.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>1383.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>1412.2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>1493.4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>1809.6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>1891.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/china_yearbook_provincial.xlsx
+++ b/output/china_yearbook_provincial.xlsx
@@ -10,15 +10,20 @@
     <sheet name="説明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="GDP 地区生产总值" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="一人当たりGDP 人均" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="小売 社会消费品零售总额" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="貿易 货物进出口" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="不動産 开发完成投资" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="全国 商品房销售面积" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="全国 商品房销售额" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="対中投資FDI(全国推移)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="対外投資ODI(全国推移)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="対中投資FDI(国別)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="対外投資ODI(国別)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="GDP産業別(省別)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="小売 社会消费品零售总额" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="貿易 货物进出口" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="不動産 开发完成投资" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="全国 商品房销售面积" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="全国 商品房销售额" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="対中投資FDI(全国推移)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="対外投資ODI(全国推移)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="対中投資FDI(国別)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="対外投資ODI(国別)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="固定資産投資(全国推移)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="固定資産投資(産業別・推移)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="輸出 貨物別" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="輸入 貨物別" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,6 +520,460 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>対中投資FDI(全国推移)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>単位: 億米ドル / 100 mil. USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年 / Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1979-1982</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>43.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>110.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>275.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>337.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>375.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>417.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>452.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>454.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>403.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>407.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>468.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>527.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>606.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>724.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>727.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>835.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>1083.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>940.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>1147.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>1239.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>1210.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>1239.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>1355.8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>1337.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>1363.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>1383.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>1412.2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>1493.4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>1809.6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>1891.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -763,7 +1222,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2438,7 +2897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3031,6 +3490,6685 @@
       </c>
       <c r="D38" s="7" t="n">
         <v>312871</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>固定資産投資(全国推移)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>年 / Year</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>全社会固定资产投资(亿元)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>全社会FAI 比上年增长(%)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发投资(亿元)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发投资 比上年增长(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>961</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v/>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>1230.4</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v/>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1430.1</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v/>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1832.9</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v/>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>2543.2</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v/>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>3120.6</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>3791.7</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>4753.8</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>257.2</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>71.581054036</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>4410.4</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>272.7</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.0264385692</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>4517</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-7.1140447378</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>5594.5</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>336.2</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>32.7279905251</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>8080.1</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>731.2</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>117.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>13072</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1937.5</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>17042</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2554.1</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>31.824516129</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>20019.3</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>3149</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>23.2919619435</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>22974</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>3216.4</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2.1403620197</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>24941.1</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>3178.4</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-1.1814450939</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>28406.2</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>3614.2292</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>13.7113012837</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>29854.7</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>4103.2</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>13.5299651375</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>32917.7</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>4984.0529</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>21.4686098655</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>37213.5</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>6344.1</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>27.2867719348</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>43499.9</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>7790.9</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>22.8054412761</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>53841.1533651068</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>23.7730508923165</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>10153.8</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>30.3289735461</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>66234.9688458192</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>23.0192235977332</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>13158.3</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>29.5899072269</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>80993.57513923739</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>22.2821970789676</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>15909.2471</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>20.9061960892</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>97583.0689087933</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>20.4824811610509</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>19422.9174</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>22.0859628391</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>118323.167481988</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>21.2537879830154</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>25288.8373</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>30.2009483651</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>144586.764998984</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>22.1964963209712</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>31203.1942</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>23.3874284268</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>181760.351068804</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>25.7102273988088</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>36241.808</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>16.1477027997</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>218833.6107</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>47951.6289081256</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>32.31025590148707</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>223646.118130458</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>61032.41247308881</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>27.27912244655076</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>263770.251274307</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>17.9409030119826</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>70643.38312225018</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>15.7473222173532</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>308312.374845071</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>16.8867123398395</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>84245.62594427486</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>19.25480097475747</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>349732.244243629</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>13.4343843380829</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>92839.49661786553</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>10.20096957826058</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>379873.016538361</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>8.618242324186481</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>93582.21259080847</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0.8000000000000256</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>406406.365364382</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>6.98479430516257</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>99841.92239953653</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>6.688995307365573</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>431526.158127829</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>6.18095455786609</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>106673.6792994978</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>6.842573475921924</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>456980.990133131</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>5.89879235032645</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>116424.8996848893</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>9.141168139531345</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>480393.463900622</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>5.12329271304478</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>127746.8101492259</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>9.724646956948234</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>493208.0893393</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>2.66752701725541</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>136438.236923405</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>6.803635068481412</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>517133.321932661</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>4.85094083217723</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>142247.7477765686</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>4.257978543379323</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>542365.7426</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>4.87928733214072</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>128074.573</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>-9.963725259700212</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>固定資産投資(産業別・推移)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>年 / Year</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>全部投资(亿元)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>第一产业(亿元)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>第二产业(亿元)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>第三产业(亿元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>44389.161215843</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>518.387251520376</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>16111.66956688</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>27759.1043974426</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>55474.9605976495</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>595.360020057379</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>21017.2534251441</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>33862.3471524481</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>68513.84448122579</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>726.675724649828</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>27588.0203273874</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>40199.1484291887</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>82830.4852808904</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>897.954669766312</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>33262.9750913028</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>48669.5555198215</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>101211.600505724</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1096.01222516124</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>41001.3056316917</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>59114.282648871</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>124433.611153207</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1587.51511804684</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>50364.8474680355</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>72481.2485671247</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>156933.340620711</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2220.47525715617</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>61177.309549726</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>93535.5558138288</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>189964.168913967</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>2492.56391229318</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>72647.08403763091</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>114824.520964043</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>214557.018130458</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>3247.53723352783</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>80392.7942102175</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>130916.686686712</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>253929.651274307</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>3885.43910508507</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>91574.4428880202</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>158469.769281202</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>297765.674845071</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>4723.31443700407</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>102729.025543312</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>190313.334864756</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>338976.444243629</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>5785.1454661228</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>112311.801077711</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>220879.497699796</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>369463.216538361</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>7081.60592244259</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>118827.237418309</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>243554.373197609</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>396441.465364382</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>8000.75784362846</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>121726.714306336</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>266713.993214417</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>421971.758127829</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>8581.50383640964</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>124420.384375337</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>288969.869916083</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>446941.990133131</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>9688.517831306461</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>132244.870838376</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>305008.601463449</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>470997.463900622</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>9741.804679378691</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>136279.687265924</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>324975.971955319</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>484844.7893393</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>11641.4565918575</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>136534.695394001</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>336668.637353442</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>508796.121932661</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>12700.8291417166</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>152356.614053081</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>343738.678737864</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>534948.2426</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>12726.2308</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>168171.1727</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>354050.8391</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D199"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>輸出 貨物別</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>数量の単位は品目名に付記。金額は万元人民币/万美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>品名 / Item</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数量 Qty</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>金額(万元)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>金額(万美元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>农产品</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>65471457</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>9807969</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>肉类(包含杂碎) (万吨)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1302213</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>194935</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>水产品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>370</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>15052326</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>2258413</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>食用水产品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>369</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>15018932</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2253396</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>蔬菜及食用菌 (万吨)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>934</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>8264761</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1236186</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>鲜或冷藏蔬菜 (万吨)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>614</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>4067185</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>606161</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>干鲜瓜果及坚果 (万吨)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>334</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>3542180</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>525431</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>苹果 (万吨)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>697651</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>104017</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>茶叶 (吨)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>375195</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>1385327</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>207854</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>粮食 (万吨)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>320</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>1244677</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>185981</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>稻谷和大米 (万吨)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>219</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>632287</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>94567</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>罐头 (吨)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>2292388</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>2849697</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>427041</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>蔬菜罐头 (吨)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>1610040</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>2096695</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>313718</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>酒类及饮料</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>2152334</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>322339</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>果蔬汁 (万吨)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>612454</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>91951</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>啤酒 (万升)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>47944</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>218562</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>32705</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>烟草及其制品 (吨)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>243908</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>501887</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>75157</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>烤烟 (吨)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>139307</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>297251</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>44737</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>卷烟 (万条)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>6143</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>91603</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>13571</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>制盐 (吨)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>1384957</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>94618</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>14129</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>水泥及水泥熟料 (万吨)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>188</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>131481</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>19472</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>钨品 (吨)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>24922</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>634938</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>95705</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>煤及褐煤 (万吨)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>816520</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>123148</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>焦炭及半焦炭 (万吨)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>892</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>2640526</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>401570</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>成品油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>5371</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>32258554</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>4814202</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>汽油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>1257</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>7736888</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1163361</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>航空煤油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>1091</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>7063112</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>1052691</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>柴油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>1093</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>7212327</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>1055699</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>氧化铝 (万吨)</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>101</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>375173</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>56750</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>稀土及其制品 (吨)</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>112793</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>3800416</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>570679</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>稀土 (吨)</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>48728</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>707091</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>106377</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>基本有机化学品</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>51408760</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>7750137</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>柠檬酸 (万吨)</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>123</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>1324832</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>200947</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>医药材及药品 (吨)</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>1620004</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>23755188</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>3603474</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>中药材 (吨)</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>134760</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>660929</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>98899</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>中式成药 (吨)</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>12837</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>250790</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>37735</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>人用疫苗 (千克)</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>830033</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>644782</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>99328</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>抗菌素(制剂除外) (吨)</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>77399</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>2846838</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>428156</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>医用敷料 (吨)</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>254142</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>1534444</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>230567</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>肥料 (万吨)</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>2481</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>7658744</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>1144691</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>尿素 (万吨)</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>283</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>1062165</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>157025</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>硫酸铵 (万吨)</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>1241</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>2164599</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>324620</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>磷酸氢二铵 (万吨)</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>358</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>1998155</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>298810</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>磷酸二氢铵 (万吨)</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>1173653</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>175842</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>合成有机染料 (吨)</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>238770</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>1012091</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>152852</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>美容化妆品及洗护用品(吨)</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>1027980</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>3757805</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>561418</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>烟花、爆竹 (吨)</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>407596</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>755660</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>114091</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>塑料制品</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>70544138</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>10583244</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>橡胶轮胎 (万吨)</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>764</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>13126848</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>1971118</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>新的充气橡胶轮胎(万吨)</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>736</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>12563523</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>1886515</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>皮革、毛皮及其制品</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>5104253</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>763561</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>裘皮服装 (吨)</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>2999</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>834779</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>122738</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>箱包及类似容器 (万吨)</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>294</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>23217275</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>3474249</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>皮革箱包及类似容器 (吨)</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>106708</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>1969458</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>296182</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>木及其制品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>1176</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>11885303</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>1790117</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>家用或装饰用木制品(万吨)</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>2318424</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>349159</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>胶合板及类似多层板(万立方米)</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>1064</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>3733216</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>562170</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>植物材料编结品 (吨)</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>296271</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>1251574</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>188929</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>纸浆、纸及其制品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>1303</v>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>20979632</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>3142486</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>纺织原料 (万吨)</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>164</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>2604366</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>391535</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>化学纤维纺织原料 (万吨)</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>155</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>1615464</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>243439</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>纺织纱线、织物及其制品</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>97764666</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>14706835</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>纺织纱线</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>9949677</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>1499810</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>纺织织物</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>47307959</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>7117289</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>纺织制品</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>40507030</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>6089736</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>服装及衣着附件</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>115838789</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>17350048</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>102358338</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>15330250</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>鞋靴 (万吨)</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>919117</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>37915467</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>5680022</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>帽类 (万个)</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>1113853</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>4435153</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>664541</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>伞 (万吨)</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>79969</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>2019379</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>303671</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>花岗岩石材及其制品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>377</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>2705508</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>401753</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>陶瓷产品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>1814</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>20943847</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>3132231</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>日用陶瓷 (万吨)</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>491</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>14480337</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>2169886</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>建筑用陶瓷 (万吨)</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>1286</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>5843162</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>869282</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>玻璃及其制品</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>17768223</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>2663525</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>珍珠、宝石及半宝石</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>2341998</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>350096</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>贵金属或包贵金属的首饰(吨)</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>788</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>10480277</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>1548345</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>铁合金 (万吨)</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>2073232</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>314247</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>钢材 (万吨)</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>6671</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>62962017</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>9461882</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>钢铁棒材 (万吨)</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>760</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>5286915</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>793129</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>角钢及型钢 (万吨)</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>360</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>2748234</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>411783</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>钢铁板材 (万吨)</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>4263</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>36065754</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>5435991</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>钢铁线材 (万吨)</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>198</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>3883665</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>581654</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>未锻轧铜及铜材 (吨)</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>915478</v>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>6307130</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>956422</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>未锻轧铝及铝材 (吨)</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="n">
+        <v>6598605</v>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>17198131</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>2596430</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>家具及其零件</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>45453154</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>6829745</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>玩具</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>31330231</v>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>4692334</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>体育用品及设备</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>11579149</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>1747030</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>笔及其零件</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>2303682</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>344403</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>机电产品</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>1356830667</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>203384274</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>机械基础件</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>21439631</v>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>3212915</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>紧固件 (吨)</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="n">
+        <v>4949901</v>
+      </c>
+      <c r="C96" s="7" t="n">
+        <v>8944112</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>1339804</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>轴承 (吨)</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="n">
+        <v>786769</v>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>3549497</v>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>533058</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>手用或机用工具 (万吨)</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="n">
+        <v>223</v>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>11201093</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>1679221</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>农业机械</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>4193490</v>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>632082</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>拖拉机 (辆)</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="n">
+        <v>128354</v>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>546277</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>81653</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>食品加工机械 (万台)</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="n">
+        <v>947</v>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>1378216</v>
+      </c>
+      <c r="D101" s="7" t="n">
+        <v>206159</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>包装机械 (台)</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="n">
+        <v>17205990</v>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>2591952</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>387755</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>印刷、装订机械及其零件</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>10583217</v>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>1585341</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>打印机、复印机及一体机 (台)</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="n">
+        <v>49863628</v>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>6086629</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>910885</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>通用机械设备</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>36849477</v>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>5535301</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>泵 (万台)</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="n">
+        <v>384153</v>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>5379778</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>807513</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>压缩机 (万台)</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="n">
+        <v>14447</v>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>5116869</v>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>770520</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>分离设备</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>3788668</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>566024</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>阀门及类似装置 (万套)</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="n">
+        <v>531110</v>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>11361277</v>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>1703837</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>纺织机械及其零件</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>3651005</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>546928</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>缝制机械及其零件</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>1629558</v>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>245249</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>机床 (台)</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="n">
+        <v>20753708</v>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>6281631</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>940568</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>自动数据处理设备及其零部件</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>156727557</v>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>23554834</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>自动数据处理设备 (万台)</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="n">
+        <v>30814</v>
+      </c>
+      <c r="C114" s="7" t="n">
+        <v>89605594</v>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>13462800</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>平板电脑 (万台)</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="n">
+        <v>13079</v>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>20634986</v>
+      </c>
+      <c r="D115" s="7" t="n">
+        <v>3086473</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>笔记本电脑 (万台)</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="n">
+        <v>16560</v>
+      </c>
+      <c r="C116" s="7" t="n">
+        <v>64400766</v>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>9688975</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>中央处理部件 (万台)</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="n">
+        <v>4059</v>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>14604738</v>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>2192302</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>存储部件 (万台)</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="n">
+        <v>21149</v>
+      </c>
+      <c r="C118" s="7" t="n">
+        <v>9143187</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>1371412</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>自动数据处理设备的零件、</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="n">
+        <v>546077</v>
+      </c>
+      <c r="C119" s="7" t="n">
+        <v>22363501</v>
+      </c>
+      <c r="D119" s="7" t="n">
+        <v>3357923</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>附件 (吨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>液晶监视器 (万台)</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="n">
+        <v>10527</v>
+      </c>
+      <c r="C121" s="7" t="n">
+        <v>9106849</v>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>1383651</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>电工器材</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>116765926</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>17443795</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>变压器 (万个)</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="n">
+        <v>321829</v>
+      </c>
+      <c r="C123" s="7" t="n">
+        <v>2955229</v>
+      </c>
+      <c r="D123" s="7" t="n">
+        <v>441900</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>原电池 (亿个)</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="n">
+        <v>292</v>
+      </c>
+      <c r="C124" s="7" t="n">
+        <v>1577968</v>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>236976</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>蓄电池 (万个)</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="n">
+        <v>442517</v>
+      </c>
+      <c r="C125" s="7" t="n">
+        <v>37264706</v>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>5542712</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>锂离子蓄电池 (万个)</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="n">
+        <v>376912</v>
+      </c>
+      <c r="C126" s="7" t="n">
+        <v>34248991</v>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>5089401</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>电气控制装置</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="n">
+        <v>23862107</v>
+      </c>
+      <c r="D127" s="7" t="n">
+        <v>3571400</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>高压开关及控制装置</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="n">
+        <v>1742832</v>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>260072</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>低压开关及控制装置</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="n">
+        <v>22119275</v>
+      </c>
+      <c r="D129" s="7" t="n">
+        <v>3311328</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>电线及电缆 (万吨)</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="n">
+        <v>227</v>
+      </c>
+      <c r="C130" s="7" t="n">
+        <v>16874812</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>2532733</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>手机 (万台)</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="n">
+        <v>82178</v>
+      </c>
+      <c r="C131" s="7" t="n">
+        <v>95265999</v>
+      </c>
+      <c r="D131" s="7" t="n">
+        <v>14265716</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>家用电器 (万台)</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="n">
+        <v>334943</v>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>56350333</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>8481247</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>电扇 (万台)</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="n">
+        <v>34706</v>
+      </c>
+      <c r="C133" s="7" t="n">
+        <v>3708035</v>
+      </c>
+      <c r="D133" s="7" t="n">
+        <v>562175</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>空调 (万台)</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="n">
+        <v>4590</v>
+      </c>
+      <c r="C134" s="7" t="n">
+        <v>5047837</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>769706</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>冰箱 (万台)</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="n">
+        <v>5486</v>
+      </c>
+      <c r="C135" s="7" t="n">
+        <v>5154685</v>
+      </c>
+      <c r="D135" s="7" t="n">
+        <v>778949</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>洗衣机 (万台)</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="n">
+        <v>2060</v>
+      </c>
+      <c r="C136" s="7" t="n">
+        <v>1921347</v>
+      </c>
+      <c r="D136" s="7" t="n">
+        <v>287980</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>吸尘器 (万台)</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="n">
+        <v>12134</v>
+      </c>
+      <c r="C137" s="7" t="n">
+        <v>3536151</v>
+      </c>
+      <c r="D137" s="7" t="n">
+        <v>530581</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>微波炉 (万个)</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="n">
+        <v>6051</v>
+      </c>
+      <c r="C138" s="7" t="n">
+        <v>2273215</v>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>343043</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>电视机 (万台)</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="n">
+        <v>9290</v>
+      </c>
+      <c r="C139" s="7" t="n">
+        <v>8467206</v>
+      </c>
+      <c r="D139" s="7" t="n">
+        <v>1272935</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>液晶电视机 (万台)</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="n">
+        <v>9218</v>
+      </c>
+      <c r="C140" s="7" t="n">
+        <v>8275056</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>1244104</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>音视频设备及其零件</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="n">
+        <v>25081434</v>
+      </c>
+      <c r="D141" s="7" t="n">
+        <v>3759087</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>电视摄像机，数字照相机及</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="n">
+        <v>42009</v>
+      </c>
+      <c r="C142" s="7" t="n">
+        <v>7030846</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>1053280</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>视频摄录一体机 (万台)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>数字照相机 (万台)</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="n">
+        <v>1154</v>
+      </c>
+      <c r="C144" s="7" t="n">
+        <v>707257</v>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>105631</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>无线电广播接收设备 (万台)</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="n">
+        <v>19797</v>
+      </c>
+      <c r="C145" s="7" t="n">
+        <v>2196660</v>
+      </c>
+      <c r="D145" s="7" t="n">
+        <v>328578</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>音视频设备的零件</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="n">
+        <v>7519726</v>
+      </c>
+      <c r="D146" s="7" t="n">
+        <v>1126192</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>有机发光二极管显示屏(万块)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>电子元件</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="n">
+        <v>187792225</v>
+      </c>
+      <c r="D148" s="7" t="n">
+        <v>28181474</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>印刷电路 (亿块)</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="n">
+        <v>433</v>
+      </c>
+      <c r="C149" s="7" t="n">
+        <v>13102850</v>
+      </c>
+      <c r="D149" s="7" t="n">
+        <v>1969706</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>二极管及类似半导体器件(亿个)</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="n">
+        <v>6545</v>
+      </c>
+      <c r="C150" s="7" t="n">
+        <v>42725533</v>
+      </c>
+      <c r="D150" s="7" t="n">
+        <v>6416686</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>太阳能电池 (万个)</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="n">
+        <v>407091</v>
+      </c>
+      <c r="C151" s="7" t="n">
+        <v>30829105</v>
+      </c>
+      <c r="D151" s="7" t="n">
+        <v>4634405</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>集成电路 (亿个)</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="n">
+        <v>2731</v>
+      </c>
+      <c r="C152" s="7" t="n">
+        <v>101726551</v>
+      </c>
+      <c r="D152" s="7" t="n">
+        <v>15273828</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>集装箱 (万个)</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="n">
+        <v>321</v>
+      </c>
+      <c r="C153" s="7" t="n">
+        <v>9662477</v>
+      </c>
+      <c r="D153" s="7" t="n">
+        <v>1467107</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>摩托车 (万辆)</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="n">
+        <v>2641</v>
+      </c>
+      <c r="C154" s="7" t="n">
+        <v>7927295</v>
+      </c>
+      <c r="D154" s="7" t="n">
+        <v>1192735</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>内燃机摩托车 (万辆)</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="n">
+        <v>1012</v>
+      </c>
+      <c r="C155" s="7" t="n">
+        <v>4362208</v>
+      </c>
+      <c r="D155" s="7" t="n">
+        <v>657163</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>电动摩托车及脚踏车 (万辆)</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="n">
+        <v>1612</v>
+      </c>
+      <c r="C156" s="7" t="n">
+        <v>3540931</v>
+      </c>
+      <c r="D156" s="7" t="n">
+        <v>531987</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>自行车 (万辆)</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="n">
+        <v>4128</v>
+      </c>
+      <c r="C157" s="7" t="n">
+        <v>2408512</v>
+      </c>
+      <c r="D157" s="7" t="n">
+        <v>363410</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>摩托车及自行车的零配件</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="n">
+        <v>8708700</v>
+      </c>
+      <c r="D158" s="7" t="n">
+        <v>1305755</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>汽车(包含底盘) (万辆)</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="n">
+        <v>332</v>
+      </c>
+      <c r="C159" s="7" t="n">
+        <v>40523967</v>
+      </c>
+      <c r="D159" s="7" t="n">
+        <v>6012536</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>乘用车 (辆)</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="n">
+        <v>2668260</v>
+      </c>
+      <c r="C160" s="7" t="n">
+        <v>28648530</v>
+      </c>
+      <c r="D160" s="7" t="n">
+        <v>4242845</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>商用车 (辆)</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="n">
+        <v>648855</v>
+      </c>
+      <c r="C161" s="7" t="n">
+        <v>11875437</v>
+      </c>
+      <c r="D161" s="7" t="n">
+        <v>1769691</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>客车(十座及以上) (辆)</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="n">
+        <v>48316</v>
+      </c>
+      <c r="C162" s="7" t="n">
+        <v>1762448</v>
+      </c>
+      <c r="D162" s="7" t="n">
+        <v>261482</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>货车 (辆)</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="n">
+        <v>491488</v>
+      </c>
+      <c r="C163" s="7" t="n">
+        <v>5831840</v>
+      </c>
+      <c r="D163" s="7" t="n">
+        <v>870041</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>专用汽车 (辆)</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="n">
+        <v>23915</v>
+      </c>
+      <c r="C164" s="7" t="n">
+        <v>1354873</v>
+      </c>
+      <c r="D164" s="7" t="n">
+        <v>201930</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>汽车零配件</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="n">
+        <v>53797089</v>
+      </c>
+      <c r="D165" s="7" t="n">
+        <v>8062422</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>车用发动机 (万台)</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="n">
+        <v>296</v>
+      </c>
+      <c r="C166" s="7" t="n">
+        <v>1411954</v>
+      </c>
+      <c r="D166" s="7" t="n">
+        <v>211720</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>汽车轮胎 (吨)</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="n">
+        <v>6510823</v>
+      </c>
+      <c r="C167" s="7" t="n">
+        <v>10762033</v>
+      </c>
+      <c r="D167" s="7" t="n">
+        <v>1616204</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>婴孩车及其零件 (吨)</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="n">
+        <v>221432</v>
+      </c>
+      <c r="C168" s="7" t="n">
+        <v>1103154</v>
+      </c>
+      <c r="D168" s="7" t="n">
+        <v>165696</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>船舶 (艘)</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="n">
+        <v>4015</v>
+      </c>
+      <c r="C169" s="7" t="n">
+        <v>14358967</v>
+      </c>
+      <c r="D169" s="7" t="n">
+        <v>2145145</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>液货船 (艘)</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="n">
+        <v>136</v>
+      </c>
+      <c r="C170" s="7" t="n">
+        <v>3504534</v>
+      </c>
+      <c r="D170" s="7" t="n">
+        <v>521580</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>集装箱船 (艘)</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="C171" s="7" t="n">
+        <v>2993841</v>
+      </c>
+      <c r="D171" s="7" t="n">
+        <v>444930</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>散货船 (艘)</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="n">
+        <v>295</v>
+      </c>
+      <c r="C172" s="7" t="n">
+        <v>3874221</v>
+      </c>
+      <c r="D172" s="7" t="n">
+        <v>583048</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>眼镜及其零件</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="n">
+        <v>4918392</v>
+      </c>
+      <c r="D173" s="7" t="n">
+        <v>737198</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>液晶显示板 (万个)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>计量检测分析自控仪器及器具</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="n">
+        <v>19376545</v>
+      </c>
+      <c r="D175" s="7" t="n">
+        <v>2895863</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>分析仪器 (台)</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="n">
+        <v>90247760</v>
+      </c>
+      <c r="C176" s="7" t="n">
+        <v>1632705</v>
+      </c>
+      <c r="D176" s="7" t="n">
+        <v>243911</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>医疗仪器及器械</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="n">
+        <v>12676995</v>
+      </c>
+      <c r="D177" s="7" t="n">
+        <v>1900637</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>钟表及其零件</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="n">
+        <v>3181730</v>
+      </c>
+      <c r="D178" s="7" t="n">
+        <v>476032</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>手表 (万只)</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="n">
+        <v>52371</v>
+      </c>
+      <c r="C179" s="7" t="n">
+        <v>1309789</v>
+      </c>
+      <c r="D179" s="7" t="n">
+        <v>195798</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>灯具、照明装置及其零件</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="n">
+        <v>29939077</v>
+      </c>
+      <c r="D180" s="7" t="n">
+        <v>4488800</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>游戏机及其零附件 (吨)</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="n">
+        <v>248466</v>
+      </c>
+      <c r="C181" s="7" t="n">
+        <v>12680425</v>
+      </c>
+      <c r="D181" s="7" t="n">
+        <v>1883827</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>高新技术产品</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="n">
+        <v>630739297</v>
+      </c>
+      <c r="D182" s="7" t="n">
+        <v>94669285</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>生物技术</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="n">
+        <v>1427585</v>
+      </c>
+      <c r="D183" s="7" t="n">
+        <v>216836</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>生命科学技术</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="n">
+        <v>43209338</v>
+      </c>
+      <c r="D184" s="7" t="n">
+        <v>6529440</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>光电技术</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="n">
+        <v>24266016</v>
+      </c>
+      <c r="D185" s="7" t="n">
+        <v>3647753</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>计算机与通信技术</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="n">
+        <v>353605177</v>
+      </c>
+      <c r="D186" s="7" t="n">
+        <v>53033450</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>电子技术</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="n">
+        <v>172590021</v>
+      </c>
+      <c r="D187" s="7" t="n">
+        <v>25906852</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>计算机集成制造技术</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="n">
+        <v>19283186</v>
+      </c>
+      <c r="D188" s="7" t="n">
+        <v>2886702</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>材料技术 (吨)</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="n">
+        <v>611305</v>
+      </c>
+      <c r="C189" s="7" t="n">
+        <v>8905823</v>
+      </c>
+      <c r="D189" s="7" t="n">
+        <v>1332777</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>航空航天技术</t>
+        </is>
+      </c>
+      <c r="C190" s="7" t="n">
+        <v>6651420</v>
+      </c>
+      <c r="D190" s="7" t="n">
+        <v>995392</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>其他技术</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="n">
+        <v>800730</v>
+      </c>
+      <c r="D191" s="7" t="n">
+        <v>120083</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>电动载人汽车 (辆)</t>
+        </is>
+      </c>
+      <c r="B192" s="7" t="n">
+        <v>1061048</v>
+      </c>
+      <c r="C192" s="7" t="n">
+        <v>16351821</v>
+      </c>
+      <c r="D192" s="7" t="n">
+        <v>2412048</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>混合动力客车(10座及以上)(辆)</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="n">
+        <v>768</v>
+      </c>
+      <c r="C193" s="7" t="n">
+        <v>71841</v>
+      </c>
+      <c r="D193" s="7" t="n">
+        <v>10505</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>纯电动客车(10座及以上) (辆)</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="n">
+        <v>6797</v>
+      </c>
+      <c r="C194" s="7" t="n">
+        <v>754820</v>
+      </c>
+      <c r="D194" s="7" t="n">
+        <v>111401</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>非插电式混合动力乘用车 (辆)</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="n">
+        <v>17113</v>
+      </c>
+      <c r="C195" s="7" t="n">
+        <v>197812</v>
+      </c>
+      <c r="D195" s="7" t="n">
+        <v>28971</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>插电式混合动力乘用车 (辆)</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="n">
+        <v>94447</v>
+      </c>
+      <c r="C196" s="7" t="n">
+        <v>1705826</v>
+      </c>
+      <c r="D196" s="7" t="n">
+        <v>252825</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>纯电动乘用车 (辆)</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="n">
+        <v>941923</v>
+      </c>
+      <c r="C197" s="7" t="n">
+        <v>13621521</v>
+      </c>
+      <c r="D197" s="7" t="n">
+        <v>2008347</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>文化产品</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="n">
+        <v>106808252</v>
+      </c>
+      <c r="D198" s="7" t="n">
+        <v>15965497</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="n">
+        <v>50833837</v>
+      </c>
+      <c r="D199" s="7" t="n">
+        <v>7612581</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D169"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>輸入 貨物別</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>数量の単位は品目名に付記。金額は万元人民币/万美元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>品名 / Item</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>数量 Qty</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>金額(万元)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>金額(万美元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>农产品</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>157240378</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>23570810</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>肉类(包含杂碎) (万吨)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>740</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>21200277</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>3172831</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>牛肉及牛杂碎 (万吨)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>273</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>12028051</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1799855</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>牛肉 (万吨)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>269</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>11866161</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1775493</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>猪肉及猪杂碎 (万吨)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>286</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>4528899</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>676073</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>猪肉 (万吨)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>176</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>2615017</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>389733</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>羊肉 (吨)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>357861</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>1373373</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>207595</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>禽肉 (吨)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>583568</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>941042</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>141275</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>水产品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>453</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>13271710</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1982807</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>食用水产品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>437</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>12973802</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1938336</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>冻鱼 (万吨)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>206</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>3419503</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>509995</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>乳品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>327</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>9260761</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1392547</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>奶粉 (万吨)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>5877204</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>885472</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>干鲜瓜果及坚果 (万吨)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>753</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>10418583</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>1571625</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>粮食 (万吨)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>14632</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>54789073</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>8230931</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>薯类 (吨)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>407</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>谷物及谷物粉 (万吨)</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>5319</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>12981001</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>1964555</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>小麦 (万吨)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>996</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>2557852</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>383671</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>大麦 (万吨)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>576</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>1354219</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>205233</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>玉米 (万吨)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>2062</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>4672940</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>710187</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>稻谷及大米 (万吨)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>619</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>1765565</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>266290</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>高粱 (万吨)</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>1014</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>2464158</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>374295</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>豆类 (万吨)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>9312</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>41795893</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>6264556</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>大豆 (万吨)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>9053</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>40638260</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>6089854</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>食用油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>822</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>7953285</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>1179911</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>食用植物油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>648</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>6063776</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>897634</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>豆油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>323613</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>47859</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>棕榈油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>341</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>2725900</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>400373</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>菜子油及芥子油(万吨)</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>1105512</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>165444</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>食糖 (万吨)</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>527</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>1725692</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>256376</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>酒类及饮料</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>3988653</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>594200</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>啤酒 (万升)</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>48204</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>434304</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>65015</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>葡萄酒 (万升)</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>33672</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>953709</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>142960</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>制盐 (吨)</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>9552650</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>374246</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>56041</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>金属矿及矿砂 (万吨)</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>135494</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>149193726</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>22465524</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>铁矿砂及其精矿 (万吨)</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>110617</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>84768873</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>12772880</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>铜矿砂及其精矿 (万吨)</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>2523</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>37128330</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>5599042</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>铝矿砂及其精矿 (万吨)</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>12528</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>4912379</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>736908</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>煤及褐煤 (万吨)</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>29320</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>28594879</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>4268329</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>原油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>50823</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>243673326</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>36572586</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>成品油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>2645</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>13103095</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>1962782</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>石脑油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>926</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>4772583</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>711390</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>航空煤油 (万吨)</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>558459</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>84571</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>天然气 (万吨)</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>10917</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>46835097</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>7003176</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>液化天然气 (万吨)</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>6336</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>34871745</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>5217898</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>气态天然气 (万吨)</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>4581</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>11963352</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>1785278</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>多晶硅 (吨)</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>87913</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>1777373</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>265016</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>基本有机化学品</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>38045030</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>5726222</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>二甲苯 (万吨)</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>1069</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>7722148</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>1165013</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>乙二醇 (万吨)</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>751</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>2966871</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>449361</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>医药材及药品 (吨)</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>311550</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>32169567</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>4803710</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>中药材 (吨)</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>131240</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>255679</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>38147</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>人用疫苗 (千克)</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>1300619</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>2638958</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>393506</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>肥料 (万吨)</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>894</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>3283830</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>491414</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>氯化钾 (万吨)</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>793</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>2810942</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>419900</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>氮磷钾三元复合肥(万吨)</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>339970</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>51698</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>美容化妆品及洗护用品(吨)</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>417895</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>14864124</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>2225530</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>初级形状的塑料 (万吨)</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>3057</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>37336261</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>5615347</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>塑料制品</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>13038401</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>1959856</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>天然及合成橡胶(包括胶乳) (万吨)</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>736</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>8632568</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1295321</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>皮革、毛皮及其制品</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>3952028</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>592011</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>牛皮革及马皮革 (吨)</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>509742</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>1123533</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>169410</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>木及其制品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>5728</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>11948884</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>1797811</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>原木 (万立方米)</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>4360</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>5663082</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>853201</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>锯材 (万立方米)</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>2647</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>5010418</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>752848</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>纸浆、纸及其制品 (万吨)</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>3811</v>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>19576098</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>2932687</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>纸浆 (万吨)</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>2916</v>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>14924291</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>2234906</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>纺织原料 (万吨)</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>356</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>6615454</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>994909</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>羊毛及毛条 (吨)</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>285629</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>1486566</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>223462</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>棉花 (万吨)</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>194</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>3486833</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>524590</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>纺织纱线、织物及其制品</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>7883447</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>1188185</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>纺织纱线</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>3481696</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>528016</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>棉纱线 (万吨)</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>118</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>2370051</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>360693</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>合成纤维纱线 (吨)</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>203714</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>769890</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>115801</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>服装及衣着附件</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>7047151</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>1053136</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>玻璃及其制品</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>4830106</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>725912</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>玻璃纤维及其制品 (吨)</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>129233</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>595361</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>89524</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>珍珠、宝石及半宝石</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>8996193</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>1334280</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>钻石 (千克)</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>2045</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>5661066</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>847669</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>钢材 (万吨)</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>1056</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>11354343</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>1708255</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>未锻轧铜及铜材 (吨)</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>5870442</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>36063548</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>5425021</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>未锻轧铝及铝材 (吨)</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>2391214</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>5014210</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>751440</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>机电产品</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>693285124</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>104100875</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>机械基础件</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>7351354</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>1103929</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>农业机械</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>612727</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>91839</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>收获机械 (台)</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="n">
+        <v>2816</v>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>281434</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>42170</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>拖拉机 (辆)</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="n">
+        <v>703</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>49818</v>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>7474</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>食品加工机械 (万台)</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>435689</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>64918</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>包装机械 (台)</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="n">
+        <v>49271</v>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>1097186</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>164918</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>印刷、装订机械及其零件</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>4195947</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>628482</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>打印机、复印机及一体机 (台)</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="n">
+        <v>10615533</v>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>1662757</v>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>248864</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>通用机械设备</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="n">
+        <v>14275442</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>2142764</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>泵 (万台)</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="n">
+        <v>9496</v>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>3030239</v>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>454438</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>压缩机 (万台)</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="n">
+        <v>718</v>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>1312170</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>196783</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>分离设备</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>2533750</v>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>380608</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>阀门及类似装置 (万套)</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="n">
+        <v>108501</v>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>5513008</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>826885</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>机床 (台)</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="n">
+        <v>91676</v>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>4772863</v>
+      </c>
+      <c r="D101" s="7" t="n">
+        <v>715335</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>自动数据处理设备及其零部件</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>37660795</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>5672656</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>自动数据处理设备 (万台)</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="n">
+        <v>138</v>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>774884</v>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>115955</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>中央处理部件 (万台)</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="n">
+        <v>1070</v>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>2111000</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>316490</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>存储部件 (万台)</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="n">
+        <v>27946</v>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>15223090</v>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>2296996</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>自动数据处理设备的零件、附件(吨)</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="n">
+        <v>47661</v>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>14661906</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>2207875</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>半导体制造设备 (台)</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="n">
+        <v>73098</v>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>19118578</v>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>2881710</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>制造单晶柱或晶圆用的机器及</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="n">
+        <v>3262</v>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>1143861</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>172084</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>装置 (台)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>制造半导体器件或集成电路用的机</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="n">
+        <v>15656</v>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>12425735</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>1870476</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>器及装置 (台)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>制造平板显示器用的机器及装置(台)</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="n">
+        <v>9483</v>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>2388877</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>361895</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>电工器材</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>28830529</v>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>4326427</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>变压器 (万个)</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="n">
+        <v>93137</v>
+      </c>
+      <c r="C114" s="7" t="n">
+        <v>468409</v>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>70356</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>蓄电池 (万个)</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="n">
+        <v>114780</v>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>2261504</v>
+      </c>
+      <c r="D115" s="7" t="n">
+        <v>340067</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>锂离子蓄电池 (万个)</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="n">
+        <v>110862</v>
+      </c>
+      <c r="C116" s="7" t="n">
+        <v>1984833</v>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>298425</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>电气控制装置</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>14318054</v>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>2148532</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>电线及电缆 (万吨)</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C118" s="7" t="n">
+        <v>3618374</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>542260</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>家用电器 (万台)</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="n">
+        <v>2881</v>
+      </c>
+      <c r="C119" s="7" t="n">
+        <v>1810030</v>
+      </c>
+      <c r="D119" s="7" t="n">
+        <v>271948</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>电视机 (万台)</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="C120" s="7" t="n">
+        <v>134771</v>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>20406</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>液晶电视机 (万台)</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="C121" s="7" t="n">
+        <v>133180</v>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>20167</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>音视频设备及其零件</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>13026846</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>1940129</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>电视摄像机,数字照相机及视频</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="n">
+        <v>3024</v>
+      </c>
+      <c r="C123" s="7" t="n">
+        <v>1603276</v>
+      </c>
+      <c r="D123" s="7" t="n">
+        <v>240206</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>摄录一体机 (万台)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>音视频设备的零件</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="n">
+        <v>11165443</v>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>1661617</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>有机发光二极管显示屏(万块)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>电子元件</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="n">
+        <v>316238871</v>
+      </c>
+      <c r="D127" s="7" t="n">
+        <v>47504899</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>电容器 (万吨)</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C128" s="7" t="n">
+        <v>6801772</v>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>1023964</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>印刷电路 (亿块)</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="n">
+        <v>354</v>
+      </c>
+      <c r="C129" s="7" t="n">
+        <v>7133002</v>
+      </c>
+      <c r="D129" s="7" t="n">
+        <v>1071682</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>二极管及类似半导体器件(亿个)</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="n">
+        <v>5960</v>
+      </c>
+      <c r="C130" s="7" t="n">
+        <v>19325938</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>2898681</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>集成电路 (亿个)</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="n">
+        <v>5380</v>
+      </c>
+      <c r="C131" s="7" t="n">
+        <v>275954304</v>
+      </c>
+      <c r="D131" s="7" t="n">
+        <v>41459934</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>汽车(包含底盘) (万辆)</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>35287361</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>5323375</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>乘用车 (辆)</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="n">
+        <v>863852</v>
+      </c>
+      <c r="C133" s="7" t="n">
+        <v>34632134</v>
+      </c>
+      <c r="D133" s="7" t="n">
+        <v>5225868</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>商用车 (辆)</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="n">
+        <v>13657</v>
+      </c>
+      <c r="C134" s="7" t="n">
+        <v>655227</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>97507</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>货车 (辆)</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="n">
+        <v>11512</v>
+      </c>
+      <c r="C135" s="7" t="n">
+        <v>514013</v>
+      </c>
+      <c r="D135" s="7" t="n">
+        <v>76193</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>专用汽车 (辆)</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="C136" s="7" t="n">
+        <v>54219</v>
+      </c>
+      <c r="D136" s="7" t="n">
+        <v>8228</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>汽车零配件</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="n">
+        <v>20740608</v>
+      </c>
+      <c r="D137" s="7" t="n">
+        <v>3123056</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>车用发动机 (万台)</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C138" s="7" t="n">
+        <v>593032</v>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>88935</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>汽车轮胎 (吨)</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="n">
+        <v>96150</v>
+      </c>
+      <c r="C139" s="7" t="n">
+        <v>397434</v>
+      </c>
+      <c r="D139" s="7" t="n">
+        <v>59968</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>飞机及其他航空器 (架)</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="n">
+        <v>43643</v>
+      </c>
+      <c r="C140" s="7" t="n">
+        <v>5258705</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>775672</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>空载重量超过2吨的飞机 (架)</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="n">
+        <v>131</v>
+      </c>
+      <c r="C141" s="7" t="n">
+        <v>5182121</v>
+      </c>
+      <c r="D141" s="7" t="n">
+        <v>764186</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>航空器零部件</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="n">
+        <v>6463980</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>968735</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>涡轮喷气发动机 (台)</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="n">
+        <v>754</v>
+      </c>
+      <c r="C143" s="7" t="n">
+        <v>2434985</v>
+      </c>
+      <c r="D143" s="7" t="n">
+        <v>365070</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>涡轮螺桨发动机 (台)</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C144" s="7" t="n">
+        <v>4089</v>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>船舶 (艘)</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="n">
+        <v>3434</v>
+      </c>
+      <c r="C145" s="7" t="n">
+        <v>682008</v>
+      </c>
+      <c r="D145" s="7" t="n">
+        <v>103697</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>计量检测分析自控仪器及器具</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="n">
+        <v>28855288</v>
+      </c>
+      <c r="D146" s="7" t="n">
+        <v>4322592</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>医疗仪器及器械</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="n">
+        <v>9605971</v>
+      </c>
+      <c r="D147" s="7" t="n">
+        <v>1436910</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>钟表及其零件</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="n">
+        <v>2846663</v>
+      </c>
+      <c r="D148" s="7" t="n">
+        <v>427183</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>手表 (万只)</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="n">
+        <v>1327</v>
+      </c>
+      <c r="C149" s="7" t="n">
+        <v>2460675</v>
+      </c>
+      <c r="D149" s="7" t="n">
+        <v>369395</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>电动手表 (万只)</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="n">
+        <v>1165</v>
+      </c>
+      <c r="C150" s="7" t="n">
+        <v>578623</v>
+      </c>
+      <c r="D150" s="7" t="n">
+        <v>86568</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>机械手表 (万只)</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="n">
+        <v>162</v>
+      </c>
+      <c r="C151" s="7" t="n">
+        <v>1882052</v>
+      </c>
+      <c r="D151" s="7" t="n">
+        <v>282827</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>高新技术产品</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="n">
+        <v>506652721</v>
+      </c>
+      <c r="D152" s="7" t="n">
+        <v>76056873</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>生物技术</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="n">
+        <v>4335785</v>
+      </c>
+      <c r="D153" s="7" t="n">
+        <v>649490</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>生命科学技术</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="n">
+        <v>34723126</v>
+      </c>
+      <c r="D154" s="7" t="n">
+        <v>5189007</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>光电技术</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="n">
+        <v>21024512</v>
+      </c>
+      <c r="D155" s="7" t="n">
+        <v>3160745</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>计算机与通信技术</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="n">
+        <v>72903909</v>
+      </c>
+      <c r="D156" s="7" t="n">
+        <v>10941079</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>电子技术</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="n">
+        <v>313119560</v>
+      </c>
+      <c r="D157" s="7" t="n">
+        <v>47031162</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>计算机集成制造技术</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="n">
+        <v>39958584</v>
+      </c>
+      <c r="D158" s="7" t="n">
+        <v>6011309</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>材料技术 (吨)</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="n">
+        <v>38122</v>
+      </c>
+      <c r="C159" s="7" t="n">
+        <v>4685992</v>
+      </c>
+      <c r="D159" s="7" t="n">
+        <v>704003</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>航空航天技术</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="n">
+        <v>14942848</v>
+      </c>
+      <c r="D160" s="7" t="n">
+        <v>2226261</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>其他技术</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="n">
+        <v>958405</v>
+      </c>
+      <c r="D161" s="7" t="n">
+        <v>143818</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>电动载人汽车 (辆)</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="n">
+        <v>132130</v>
+      </c>
+      <c r="C162" s="7" t="n">
+        <v>5101262</v>
+      </c>
+      <c r="D162" s="7" t="n">
+        <v>765952</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>混合动力客车(10座及以上) (辆)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>纯电动客车(10座及以上) (辆)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>非插电式混合动力乘用车 (辆)</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="n">
+        <v>89323</v>
+      </c>
+      <c r="C165" s="7" t="n">
+        <v>2717961</v>
+      </c>
+      <c r="D165" s="7" t="n">
+        <v>409962</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>插电式混合动力乘用车 (辆)</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="n">
+        <v>24618</v>
+      </c>
+      <c r="C166" s="7" t="n">
+        <v>1410592</v>
+      </c>
+      <c r="D166" s="7" t="n">
+        <v>211535</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>纯电动乘用车 (辆)</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="n">
+        <v>18189</v>
+      </c>
+      <c r="C167" s="7" t="n">
+        <v>972709</v>
+      </c>
+      <c r="D167" s="7" t="n">
+        <v>144456</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>文化产品</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="n">
+        <v>10635474</v>
+      </c>
+      <c r="D168" s="7" t="n">
+        <v>1587436</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="n">
+        <v>138507220</v>
+      </c>
+      <c r="D169" s="7" t="n">
+        <v>20760179</v>
       </c>
     </row>
   </sheetData>
@@ -3840,6 +10978,1454 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GDP産業別(省別)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>地区/地域</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>第一产业
+2022 値</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>第二产业
+2022 値</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>第三产业
+2022 値</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔业
+2022 値</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>工业
+2022 値</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>建筑业
+2022 値</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>批发和零售业
+2022 値</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>交通运输仓储和邮政业
+2022 値</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>住宿和餐饮业
+2022 値</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>金融业
+2022 値</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>房地产业
+2022 値</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>其他
+2022 値</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>6605.1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>34894.3</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>5036.4</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1614.2</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>3110.3</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>879.2</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>372.6</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>8196.700000000001</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>2594.5</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>19693.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>273.1</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>6038.9</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>9999.299999999999</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>5402.7</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>724.6</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1401.7</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1061.1</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>2197.3</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1020.8</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>4093.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>4410.3</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>17050.1</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>20910</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>4697.4</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>14675.3</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>2413.6</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>3429.1</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>3013.3</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>358.3</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>2931.8</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>2403.1</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>8448.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>1340.4</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>13840.8</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>10461.3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1415.4</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>12758.6</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1093.3</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1666.7</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1198.5</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>213.8</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>1359</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>1165.5</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>4771.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>内モンゴル</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>2653.7</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>11241.8</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>9263.1</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>2710</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>9703.799999999999</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1538</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1585.3</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1317.9</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>291.6</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>981.7</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>830.3</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>遼寧</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>2597.6</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>11755.8</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>14621.7</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>2685.8</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>10239.1</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1598.7</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>2229.1</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>1367.6</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>302.9</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>2138.3</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>1501.1</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>6912.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1689.1</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>4628.3</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>6752.8</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1742.3</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>3737.9</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>927.2</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>785.5</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>592.1</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>1000.4</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>706.7</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>3414.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>黒龍江</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>3609.8</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>4648.9</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>7642.2</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>3710.9</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>4257.6</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>460.3</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1294.3</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>553.1</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>210.1</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>1127.2</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>695.1</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>3592.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>11458.4</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>33097.4</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>10794.5</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>743.6</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>5068.5</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>1914.5</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>8626.299999999999</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>3619.2</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>13450.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>江蘇</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>4959.4</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>55888.7</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>62027.5</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>5369.5</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>48593.6</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>7377.8</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>13350.7</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>3655.6</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>1550.7</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>9689.9</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>7932.6</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>25355.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>2324.8</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>33205.2</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>42185.4</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>2397</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>28871.3</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>4388.1</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>9404.200000000001</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>2375.5</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>6690</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>5019.7</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>17346</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>3513.7</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>18588</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>22943.3</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>3722.3</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>13792</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>4819.4</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>4240.8</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>2171.7</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>825.9</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>2935.1</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>2937.1</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>9600.799999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>3076.2</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>25078.2</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>24955.5</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>3191.9</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>19628.8</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>5518.9</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>6230.4</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>1960</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>734.4</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>3889.8</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>2674.9</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>9280.799999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>2451.5</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>14359.6</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>15263.7</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>2577.8</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>11770.3</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>2597.2</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2844.5</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>1341.7</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>555.5</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>2140.5</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>2117.4</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>6129.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>山東</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>6298.6</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>35014.2</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>46122.3</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>6769</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>28739</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>6424.5</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>11819.1</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>4911</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>1276.2</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>5203.1</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>4406.7</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>17886.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>5817.8</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>25465</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>30062.2</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>6169.8</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>19592.8</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>5951.6</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>4496.5</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>3721.1</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>1066.5</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>3301.3</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>3631</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>13414.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>4986.7</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>21240.6</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>27507.6</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>5321.9</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>17546.3</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>3741.5</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>3593.4</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>2313.9</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>1186.5</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>3639.7</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>3909.4</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>12482.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>4602.7</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>19182.6</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>24885.1</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>4873.4</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>15025.3</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>4174.9</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>4787.1</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>1696.9</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>951.5</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>2421.5</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>2822</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>11917.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>広東</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>5340.4</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>52843.5</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>70934.7</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>5531.6</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>47723</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>5247.6</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>12319.7</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>4040.9</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>1765.2</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>11825.8</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>10450.6</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>30214.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>広西</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>4269.8</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>8938.6</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>13092.5</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>4404.2</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>6775.9</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>2180.4</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>2156.3</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>1098.3</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>385.9</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>1834.7</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>1899.3</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>5566.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1417.8</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1310.9</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>4089.5</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>1471.4</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>770.1</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>545.6</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>958.8</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>231.8</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>438.7</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>571</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>1458.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>重慶</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>2012.1</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>11693.9</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>15423.1</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>2058.6</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>8276</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>3417.9</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>2816.7</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1084</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>567.7</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>2491</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>1668.6</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>6748.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>5964.3</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>21157.1</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>29628.4</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>6133.1</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>16412.2</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>4888.6</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>5132.1</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1587.5</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>1180.1</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>3840.1</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>3446</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>14130.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>貴州</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>2861.2</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>7113</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>10190.4</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>3020.4</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>5493.1</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1626.2</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1582.2</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>838.2</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>449.4</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>1193.5</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>863.1</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>5098.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>雲南</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>4012.2</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>10471.2</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>14470.8</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>4090.1</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>7197.1</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>3282.4</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>2990.7</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>1335.4</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>653.1</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>1594.6</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>1633.6</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>6177.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>チベット</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>804.7</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>1147.8</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>200.8</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>603.9</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>215.4</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>664.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>陝西</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>2575.3</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>15933.1</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>14264.2</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>2710.6</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>13158.3</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>2893</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>2103.3</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>1293.8</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>2109.7</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>1617.9</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>6485.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>甘粛</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>1515.3</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>3945</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>5741.2</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>1561.3</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>3297.2</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>657.6</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>795.6</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>555.6</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>925.1</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>573.2</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>380.2</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1585.7</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1644.2</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>385</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1228.7</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>357</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>171.1</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>155.2</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>286.2</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>847.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>寧夏</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>407.5</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>2449.1</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>2213</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>428.5</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>2094</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>357.2</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>1166.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>2509.3</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>7271.1</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>7961</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>2654.6</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>6022.8</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>1355.7</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>784.4</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>845.3</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>1216.9</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>575.5</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>4150.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4501,7 +13087,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5065,7 +13651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5335,244 +13921,6 @@
       </c>
       <c r="B35" s="4" t="n">
         <v>1158.8633</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>全国 商品房销售面积</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>地区/地域</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-1998 値</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2000 値</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2005 値</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2006 値</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2007 値</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2008 値</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2009 値</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2010 値</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2011 値</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2012 値</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2013 値</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2014 値</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2015 値</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2016 値</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2017 値</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2018 値</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2019 値</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2020 値</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2021 値</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>商品房销售面积
-2022 値</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>全国</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>12185.3</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>18637.128</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>55486.2247</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>61857.0733</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>77354.71799999999</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>65969.83</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>94755</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>104482.7556101567</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>108662.065834563</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>110074.6726904123</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>128347.0683570207</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>118335.9970251731</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>125475.7646102896</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>152578.5297661122</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>163427.0326061051</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>164947.3403961267</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>164531.4239690406</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>168560.4128347682</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>171414.5985785524</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>129766.3947</v>
       </c>
     </row>
   </sheetData>
@@ -5615,7 +13963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>全国 商品房销售额</t>
+          <t>全国 商品房销售面积</t>
         </is>
       </c>
     </row>
@@ -5627,121 +13975,121 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 1998 値</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2000 値</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2005 値</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2006 値</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2007 値</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2008 値</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2009 値</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2010 値</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2011 値</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2012 値</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2013 値</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2014 値</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2015 値</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2016 値</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2017 値</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2018 値</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2019 値</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2020 値</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2021 値</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>商品房销售额
+          <t>商品房销售面积
 2022 値</t>
         </is>
       </c>
@@ -5753,64 +14101,64 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2513.3027</v>
+        <v>12185.3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3935.4423</v>
+        <v>18637.128</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>17576.1325</v>
+        <v>55486.2247</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>20825.9631</v>
+        <v>61857.0733</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>29889.1189</v>
+        <v>77354.71799999999</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>25068.183</v>
+        <v>65969.83</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>44355.1695</v>
+        <v>94755</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>52572.1112633444</v>
+        <v>104482.7556101567</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>58302.5964813075</v>
+        <v>108662.065834563</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>64020.5878365377</v>
+        <v>110074.6726904123</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>80531.20985644629</v>
+        <v>128347.0683570207</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>75377.2124256337</v>
+        <v>118335.9970251731</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>86010.1729437438</v>
+        <v>125475.7646102896</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>115425.652090504</v>
+        <v>152578.5297661122</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>130874.14087025</v>
+        <v>163427.0326061051</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>146129.877664702</v>
+        <v>164947.3403961267</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>155801.668860217</v>
+        <v>164531.4239690406</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>169069.013006639</v>
+        <v>168560.4128347682</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>176945.569447494</v>
+        <v>171414.5985785524</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>129655.5699</v>
+        <v>129766.3947</v>
       </c>
     </row>
   </sheetData>
@@ -5824,447 +14172,231 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>対中投資FDI(全国推移)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>単位: 億米ドル / 100 mil. USD</t>
+          <t>全国 商品房销售额</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>地区/地域</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+1998 値</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2000 値</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2005 値</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2006 値</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2007 値</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2008 値</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2009 値</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2010 値</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2011 値</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2012 値</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2013 値</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2014 値</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2015 値</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2016 値</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2017 値</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2018 値</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2019 値</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2020 値</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2021 値</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>商品房销售额
+2022 値</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>年 / Year</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1979-1982</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>17.7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>19.6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>22.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>23.1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>31.9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>33.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>34.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>43.7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>110.1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>275.1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>337.7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>375.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>417.3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>452.6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>454.6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>403.2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>407.2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>468.8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n">
-        <v>527.4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>606.3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>724.1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>727.2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>835.2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n">
-        <v>1083.1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>940.6</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>1147.3</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>1239.9</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>1210.7</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>1239.1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>1355.8</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>1337.1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>1363.2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>1383.1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>1412.2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>1493.4</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>1809.6</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>1891.3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>全国</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>2513.3027</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>3935.4423</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>17576.1325</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>20825.9631</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>29889.1189</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>25068.183</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>44355.1695</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>52572.1112633444</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>58302.5964813075</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>64020.5878365377</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>80531.20985644629</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>75377.2124256337</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>86010.1729437438</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>115425.652090504</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>130874.14087025</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>146129.877664702</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>155801.668860217</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>169069.013006639</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>176945.569447494</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>129655.5699</v>
       </c>
     </row>
   </sheetData>

--- a/output/china_yearbook_provincial.xlsx
+++ b/output/china_yearbook_provincial.xlsx
@@ -1231,10 +1231,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1271,9 +1271,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>总计</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>总计
+総計
+Grand Total</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
@@ -1284,9 +1286,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>亚洲</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>亚洲
+アジア
+Asia</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -1297,9 +1301,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>孟加拉国</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>孟加拉国
+バングラデシュ
+Bangladesh</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -1310,9 +1316,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>文莱</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>文莱
+ブルネイ
+Brunei</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -1323,9 +1331,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>缅甸</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>缅甸
+ミャンマー
+Myanmar</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
@@ -1336,9 +1346,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>柬埔寨</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>柬埔寨
+カンボジア
+Cambodia</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
@@ -1349,9 +1361,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>塞浦路斯</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>塞浦路斯
+キプロス
+Cyprus</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -1362,9 +1376,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>中国香港</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>中国香港
+香港
+Hong Kong</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -1375,9 +1391,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>印度</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>印度
+インド
+India</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -1388,9 +1406,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>印度尼西亚</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>印度尼西亚
+インドネシア
+Indonesia</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -1401,9 +1421,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>伊拉克</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>伊拉克
+イラク
+Iraq</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -1414,9 +1436,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>以色列</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>以色列
+イスラエル
+Israel</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -1427,9 +1451,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>日本</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>日本
+日本
+Japan</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -1440,9 +1466,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>约旦</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>约旦
+ヨルダン
+Jordan</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
@@ -1453,9 +1481,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>科威特</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>科威特
+クウェート
+Kuwait</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
@@ -1466,9 +1496,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>老挝</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>老挝
+ラオス
+Laos</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
@@ -1479,9 +1511,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>黎巴嫩</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>黎巴嫩
+レバノン
+Lebanon</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -1492,9 +1526,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>中国澳门</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>中国澳门
+マカオ
+Macao</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
@@ -1505,9 +1541,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>马来西亚</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>马来西亚
+マレーシア
+Malaysia</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -1518,9 +1556,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>蒙古</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>蒙古
+モンゴル
+Mongolia</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
@@ -1531,9 +1571,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>巴基斯坦</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>巴基斯坦
+パキスタン
+Pakistan</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
@@ -1544,9 +1586,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>菲律宾</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>菲律宾
+フィリピン
+Philippines</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
@@ -1557,9 +1601,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>卡塔尔</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>卡塔尔
+カタール
+Qatar</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
@@ -1570,9 +1616,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>沙特阿拉伯</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>沙特阿拉伯
+サウジアラビア
+Saudi Arabia</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
@@ -1583,9 +1631,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>新加坡</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>新加坡
+シンガポール
+Singapore</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
@@ -1596,9 +1646,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>韩国</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>韩国
+韓国
+South Korea</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
@@ -1609,9 +1661,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>斯里兰卡</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>斯里兰卡
+スリランカ
+Sri Lanka</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -1622,9 +1676,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>泰国</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>泰国
+タイ
+Thailand</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
@@ -1635,9 +1691,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>土耳其</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>土耳其
+トルコ
+Turkey</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
@@ -1648,9 +1706,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>阿联酋</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>阿联酋
+アラブ首長国連邦
+United Arab Emirates</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
@@ -1661,9 +1721,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>也门</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>也门
+イエメン
+Yemen</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
@@ -1674,9 +1736,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>越南</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>越南
+ベトナム
+Vietnam</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
@@ -1687,9 +1751,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>中国台湾</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>中国台湾
+台湾
+Taiwan</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
@@ -1700,9 +1766,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>东帝汶</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>东帝汶
+東ティモール
+East Timor</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
@@ -1713,9 +1781,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>土库曼斯坦</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>土库曼斯坦
+トルクメニスタン
+Turkmenistan</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
@@ -1726,9 +1796,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>乌兹别克斯坦</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>乌兹别克斯坦
+ウズベキスタン
+Uzbekistan</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
@@ -1739,9 +1811,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>非洲</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>非洲
+アフリカ
+Africa</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
@@ -1752,9 +1826,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>喀麦隆</t>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>喀麦隆
+カメルーン
+Cameroon</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
@@ -1765,9 +1841,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>刚果(布)</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>刚果(布)
+コンゴ共和国
+Congo (Brazzaville)</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
@@ -1778,9 +1856,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>埃及</t>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>埃及
+エジプト
+Egypt</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
@@ -1791,9 +1871,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>埃塞俄比亚</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>埃塞俄比亚
+エチオピア
+Ethiopia</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
@@ -1804,9 +1886,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>加纳</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>加纳
+ガーナ
+Ghana</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
@@ -1817,9 +1901,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>马里</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>马里
+マリ
+Mali</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
@@ -1830,9 +1916,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>毛里塔尼亚</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>毛里塔尼亚
+モーリタニア
+Mauritania</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
@@ -1843,9 +1931,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>毛里求斯</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>毛里求斯
+モーリシャス
+Mauritius</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
@@ -1856,9 +1946,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>摩洛哥</t>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>摩洛哥
+モロッコ
+Morocco</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
@@ -1869,9 +1961,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>纳米比亚</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>纳米比亚
+ナミビア
+Namibia</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
@@ -1882,9 +1976,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>塞舌尔</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>塞舌尔
+セーシェル
+Seychelles</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
@@ -1895,9 +1991,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>南非</t>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>南非
+南アフリカ
+South Africa</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
@@ -1908,9 +2006,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>坦桑尼亚</t>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>坦桑尼亚
+タンザニア
+Tanzania</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
@@ -1921,9 +2021,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>乌干达</t>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>乌干达
+ウガンダ
+Uganda</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
@@ -1934,9 +2036,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>赞比亚</t>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>赞比亚
+ザンビア
+Zambia</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
@@ -1947,9 +2051,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>非洲其他国家(地区)</t>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>非洲其他国家(地区)
+アフリカその他
+Other Africa</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
@@ -1960,9 +2066,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>欧洲</t>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>欧洲
+ヨーロッパ
+Europe</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
@@ -1973,9 +2081,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>比利时</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>比利时
+ベルギー
+Belgium</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
@@ -1986,9 +2096,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>丹麦</t>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>丹麦
+デンマーク
+Denmark</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
@@ -1999,9 +2111,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>英国</t>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>英国
+イギリス
+United Kingdom</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
@@ -2012,9 +2126,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>德国</t>
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>德国
+ドイツ
+Germany</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
@@ -2025,9 +2141,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>法国</t>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>法国
+フランス
+France</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
@@ -2038,9 +2156,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>爱尔兰</t>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>爱尔兰
+アイルランド
+Ireland</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
@@ -2051,9 +2171,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>意大利</t>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>意大利
+イタリア
+Italy</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
@@ -2064,9 +2186,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>卢森堡</t>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>卢森堡
+ルクセンブルク
+Luxembourg</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
@@ -2077,9 +2201,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>荷兰</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>荷兰
+オランダ
+Netherlands</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
@@ -2090,9 +2216,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>希腊</t>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>希腊
+ギリシャ
+Greece</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
@@ -2103,9 +2231,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>葡萄牙</t>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>葡萄牙
+ポルトガル
+Portugal</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
@@ -2116,9 +2246,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>西班牙</t>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>西班牙
+スペイン
+Spain</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
@@ -2129,9 +2261,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>安道尔</t>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>安道尔
+アンドラ
+Andorra</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
@@ -2142,9 +2276,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>奥地利</t>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>奥地利
+オーストリア
+Austria</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
@@ -2155,9 +2291,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>保加利亚</t>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>保加利亚
+ブルガリア
+Bulgaria</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
@@ -2168,9 +2306,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>芬兰</t>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>芬兰
+フィンランド
+Finland</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
@@ -2181,9 +2321,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>匈牙利</t>
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>匈牙利
+ハンガリー
+Hungary</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
@@ -2194,9 +2336,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>冰岛</t>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>冰岛
+アイスランド
+Iceland</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
@@ -2207,9 +2351,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>列支敦士登</t>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>列支敦士登
+リヒテンシュタイン
+Liechtenstein</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
@@ -2220,9 +2366,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>摩纳哥</t>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>摩纳哥
+モナコ
+Monaco</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
@@ -2233,9 +2381,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>挪威</t>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>挪威
+ノルウェー
+Norway</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
@@ -2246,9 +2396,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>波兰</t>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>波兰
+ポーランド
+Poland</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
@@ -2259,9 +2411,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>罗马尼亚</t>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>罗马尼亚
+ルーマニア
+Romania</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
@@ -2272,9 +2426,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>瑞典</t>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>瑞典
+スウェーデン
+Sweden</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
@@ -2285,9 +2441,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>瑞士</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>瑞士
+スイス
+Switzerland</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
@@ -2298,9 +2456,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>爱沙尼亚</t>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>爱沙尼亚
+エストニア
+Estonia</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
@@ -2311,9 +2471,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>立陶宛</t>
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>立陶宛
+リトアニア
+Lithuania</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
@@ -2324,9 +2486,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>阿塞拜疆</t>
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>阿塞拜疆
+アゼルバイジャン
+Azerbaijan</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
@@ -2337,9 +2501,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>白俄罗斯</t>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>白俄罗斯
+ベラルーシ
+Belarus</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
@@ -2350,9 +2516,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>俄罗斯联邦</t>
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>俄罗斯联邦
+ロシア
+Russia</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
@@ -2363,9 +2531,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>斯洛文尼亚</t>
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>斯洛文尼亚
+スロベニア
+Slovenia</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
@@ -2376,9 +2546,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>克罗地亚</t>
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>克罗地亚
+クロアチア
+Croatia</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
@@ -2389,9 +2561,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>捷克</t>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>捷克
+チェコ
+Czech Republic</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
@@ -2402,9 +2576,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>斯洛伐克</t>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>斯洛伐克
+スロバキア
+Slovakia</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
@@ -2415,9 +2591,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>塞尔维亚</t>
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>塞尔维亚
+セルビア
+Serbia</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
@@ -2428,9 +2606,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>欧洲其他国家(地区)</t>
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>欧洲其他国家(地区)
+欧州その他
+Other Europe</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
@@ -2441,9 +2621,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>拉丁美洲</t>
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>拉丁美洲
+ラテンアメリカ
+Latin America</t>
         </is>
       </c>
       <c r="B95" s="8" t="n">
@@ -2454,9 +2636,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>安提瓜和巴布达</t>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>安提瓜和巴布达
+アンティグア・バーブーダ
+Antigua and Barbuda</t>
         </is>
       </c>
       <c r="B96" s="8" t="n">
@@ -2467,9 +2651,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>阿根廷</t>
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>阿根廷
+アルゼンチン
+Argentina</t>
         </is>
       </c>
       <c r="B97" s="8" t="n">
@@ -2480,9 +2666,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>巴巴多斯</t>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>巴巴多斯
+バルバドス
+Barbados</t>
         </is>
       </c>
       <c r="B98" s="8" t="n">
@@ -2493,9 +2681,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>伯利兹</t>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>伯利兹
+ベリーズ
+Belize</t>
         </is>
       </c>
       <c r="B99" s="8" t="n">
@@ -2506,9 +2696,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>巴西</t>
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>巴西
+ブラジル
+Brazil</t>
         </is>
       </c>
       <c r="B100" s="8" t="n">
@@ -2519,9 +2711,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>开曼群岛</t>
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>开曼群岛
+ケイマン諸島
+Cayman Islands</t>
         </is>
       </c>
       <c r="B101" s="8" t="n">
@@ -2532,9 +2726,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>智利</t>
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>智利
+チリ
+Chile</t>
         </is>
       </c>
       <c r="B102" s="8" t="n">
@@ -2545,9 +2741,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>古巴</t>
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>古巴
+キューバ
+Cuba</t>
         </is>
       </c>
       <c r="B103" s="8" t="n">
@@ -2558,9 +2756,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>多米尼加共和国</t>
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>多米尼加共和国
+ドミニカ共和国
+Dominican Republic</t>
         </is>
       </c>
       <c r="B104" s="8" t="n">
@@ -2571,9 +2771,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>危地马拉</t>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>危地马拉
+グアテマラ
+Guatemala</t>
         </is>
       </c>
       <c r="B105" s="8" t="n">
@@ -2584,9 +2786,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>圭亚那</t>
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>圭亚那
+ガイアナ
+Guyana</t>
         </is>
       </c>
       <c r="B106" s="8" t="n">
@@ -2597,9 +2801,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>墨西哥</t>
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>墨西哥
+メキシコ
+Mexico</t>
         </is>
       </c>
       <c r="B107" s="8" t="n">
@@ -2610,9 +2816,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>巴拿马</t>
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>巴拿马
+パナマ
+Panama</t>
         </is>
       </c>
       <c r="B108" s="8" t="n">
@@ -2623,9 +2831,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>秘鲁</t>
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>秘鲁
+ペルー
+Peru</t>
         </is>
       </c>
       <c r="B109" s="8" t="n">
@@ -2636,9 +2846,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>特立尼达和多巴哥</t>
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>特立尼达和多巴哥
+トリニダード・トバゴ
+Trinidad and Tobago</t>
         </is>
       </c>
       <c r="B110" s="8" t="n">
@@ -2649,9 +2861,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>特克斯和凯科斯群岛</t>
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>特克斯和凯科斯群岛
+タークス・カイコス諸島
+Turks and Caicos</t>
         </is>
       </c>
       <c r="B111" s="8" t="n">
@@ -2662,9 +2876,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>乌拉圭</t>
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>乌拉圭
+ウルグアイ
+Uruguay</t>
         </is>
       </c>
       <c r="B112" s="8" t="n">
@@ -2675,9 +2891,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>委内瑞拉</t>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>委内瑞拉
+ベネズエラ
+Venezuela</t>
         </is>
       </c>
       <c r="B113" s="8" t="n">
@@ -2688,9 +2906,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>英属维尔京群岛</t>
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>英属维尔京群岛
+英領ヴァージン諸島
+British Virgin Islands</t>
         </is>
       </c>
       <c r="B114" s="8" t="n">
@@ -2701,9 +2921,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>圣其茨和尼维斯</t>
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>圣其茨和尼维斯
+セントクリストファー・ネイビス
+Saint Kitts and Nevis</t>
         </is>
       </c>
       <c r="B115" s="8" t="n">
@@ -2714,9 +2936,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>拉丁美洲其他国家(地区)</t>
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>拉丁美洲其他国家(地区)
+ラテンアメリカその他
+Other Latin America</t>
         </is>
       </c>
       <c r="B116" s="8" t="n">
@@ -2727,9 +2951,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>北美洲</t>
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>北美洲
+北米
+North America</t>
         </is>
       </c>
       <c r="B117" s="8" t="n">
@@ -2740,9 +2966,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>加拿大</t>
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>加拿大
+カナダ
+Canada</t>
         </is>
       </c>
       <c r="B118" s="8" t="n">
@@ -2753,9 +2981,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>美国</t>
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>美国
+アメリカ合衆国
+United States</t>
         </is>
       </c>
       <c r="B119" s="8" t="n">
@@ -2766,9 +2996,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>百慕大</t>
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>百慕大
+バミューダ
+Bermuda</t>
         </is>
       </c>
       <c r="B120" s="8" t="n">
@@ -2779,9 +3011,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>大洋洲</t>
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>大洋洲
+オセアニア
+Oceania</t>
         </is>
       </c>
       <c r="B121" s="8" t="n">
@@ -2792,9 +3026,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>澳大利亚</t>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>澳大利亚
+オーストラリア
+Australia</t>
         </is>
       </c>
       <c r="B122" s="8" t="n">
@@ -2805,9 +3041,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>库克群岛</t>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>库克群岛
+クック諸島
+Cook Islands</t>
         </is>
       </c>
       <c r="B123" s="8" t="n">
@@ -2818,9 +3056,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>新西兰</t>
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>新西兰
+ニュージーランド
+New Zealand</t>
         </is>
       </c>
       <c r="B124" s="8" t="n">
@@ -2831,9 +3071,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>萨摩亚</t>
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>萨摩亚
+サモア
+Samoa</t>
         </is>
       </c>
       <c r="B125" s="8" t="n">
@@ -2844,9 +3086,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>马绍尔群岛</t>
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>马绍尔群岛
+マーシャル諸島
+Marshall Islands</t>
         </is>
       </c>
       <c r="B126" s="8" t="n">
@@ -2857,9 +3101,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>大洋洲其他国家(地区)</t>
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>大洋洲其他国家(地区)
+オセアニアその他
+Other Oceania</t>
         </is>
       </c>
       <c r="B127" s="8" t="n">
@@ -2870,9 +3116,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>其他</t>
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>其他
+その他
+Others</t>
         </is>
       </c>
       <c r="B128" s="8" t="n">
@@ -2880,19 +3128,6 @@
       </c>
       <c r="C128" s="8" t="n">
         <v>86</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>注：2021年各国家(地区)数据不包含银行、证券、保险领域数据。</t>
-        </is>
-      </c>
-      <c r="B129" s="8" t="n">
-        <v/>
-      </c>
-      <c r="C129" s="8" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -2909,7 +3144,7 @@
   <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -2952,9 +3187,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>合计</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>合计
+合計
+Total</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
@@ -2968,9 +3205,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>亚洲</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>亚洲
+アジア
+Asia</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -2984,9 +3223,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>中国香港</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>中国香港
+香港
+Hong Kong</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -3000,9 +3241,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>印度</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>印度
+インド
+India</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -3016,9 +3259,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>印度尼西亚</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>印度尼西亚
+インドネシア
+Indonesia</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
@@ -3032,9 +3277,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>日本</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>日本
+日本
+Japan</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
@@ -3048,9 +3295,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>中国澳门</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>中国澳门
+マカオ
+Macao</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -3064,9 +3313,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>新加坡</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>新加坡
+シンガポール
+Singapore</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -3080,9 +3331,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>韩国</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>韩国
+韓国
+South Korea</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -3096,9 +3349,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>泰国</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>泰国
+タイ
+Thailand</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -3112,9 +3367,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>越南</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>越南
+ベトナム
+Vietnam</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -3128,9 +3385,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>非洲</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>非洲
+アフリカ
+Africa</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -3144,9 +3403,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>阿尔及利亚</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>阿尔及利亚
+アルジェリア
+Algeria</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -3160,9 +3421,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>苏丹</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>苏丹
+スーダン
+Sudan</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
@@ -3176,9 +3439,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>几内亚</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>几内亚
+ギニア
+Guinea</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
@@ -3192,9 +3457,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>马达加斯加</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>马达加斯加
+マダガスカル
+Madagascar</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
@@ -3208,9 +3475,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>尼日利亚</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>尼日利亚
+ナイジェリア
+Nigeria</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -3224,9 +3493,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>南非</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>南非
+南アフリカ
+South Africa</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
@@ -3240,9 +3511,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>欧洲</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>欧洲
+ヨーロッパ
+Europe</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -3256,9 +3529,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>英国</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>英国
+イギリス
+United Kingdom</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
@@ -3272,9 +3547,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>德国</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>德国
+ドイツ
+Germany</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
@@ -3288,9 +3565,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>法国</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>法国
+フランス
+France</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
@@ -3304,9 +3583,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>俄罗斯联邦</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>俄罗斯联邦
+ロシア
+Russia</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
@@ -3320,9 +3601,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>拉丁美洲</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>拉丁美洲
+ラテンアメリカ
+Latin America</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
@@ -3336,9 +3619,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>巴西</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>巴西
+ブラジル
+Brazil</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
@@ -3352,9 +3637,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>开曼群岛</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>开曼群岛
+ケイマン諸島
+Cayman Islands</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
@@ -3368,9 +3655,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>墨西哥</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>墨西哥
+メキシコ
+Mexico</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -3384,9 +3673,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>英属维尔京群岛</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>英属维尔京群岛
+英領ヴァージン諸島
+British Virgin Islands</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
@@ -3400,9 +3691,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>北美洲</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>北美洲
+北米
+North America</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
@@ -3416,9 +3709,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>加拿大</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>加拿大
+カナダ
+Canada</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
@@ -3432,9 +3727,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>美国</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>美国
+アメリカ合衆国
+United States</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
@@ -3448,9 +3745,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>大洋洲</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>大洋洲
+オセアニア
+Oceania</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
@@ -3464,9 +3763,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>澳大利亚</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>澳大利亚
+オーストラリア
+Australia</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
@@ -3480,9 +3781,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>新西兰</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>新西兰
+ニュージーランド
+New Zealand</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
@@ -4686,7 +4989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4712,7 +5015,9 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>品名 / Item</t>
+          <t>品名
+品目
+Item</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -4732,9 +5037,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>农产品</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>农产品
+農産物
+Agricultural products</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -4745,9 +5052,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>肉类(包含杂碎) (万吨)</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>肉类(包含杂碎) (万吨)
+肉類(雑品含む)
+Meat (incl. offal)</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -4761,9 +5070,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>水产品 (万吨)</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>水产品 (万吨)
+水産物
+Aquatic products</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -4777,9 +5088,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>食用水产品 (万吨)</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>食用水产品 (万吨)
+食用水産物
+Edible aquatic products</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -4793,9 +5106,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>蔬菜及食用菌 (万吨)</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>蔬菜及食用菌 (万吨)
+野菜・食用きのこ
+Vegetables &amp; edible fungi</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
@@ -4809,9 +5124,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>鲜或冷藏蔬菜 (万吨)</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>鲜或冷藏蔬菜 (万吨)
+生鮮・冷蔵野菜
+Fresh/chilled vegetables</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
@@ -4825,9 +5142,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>干鲜瓜果及坚果 (万吨)</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>干鲜瓜果及坚果 (万吨)
+果実・ナッツ
+Fruits &amp; nuts</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -4841,9 +5160,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>苹果 (万吨)</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>苹果 (万吨)
+りんご
+Apples</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -4857,9 +5178,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>茶叶 (吨)</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>茶叶 (吨)
+茶
+Tea</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -4873,9 +5196,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>粮食 (万吨)</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>粮食 (万吨)
+食糧
+Grain</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -4889,9 +5214,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>稻谷和大米 (万吨)</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>稻谷和大米 (万吨)
+もみ・米
+Paddy &amp; rice</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -4905,9 +5232,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>罐头 (吨)</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>罐头 (吨)
+缶詰
+Canned food</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -4921,9 +5250,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>蔬菜罐头 (吨)</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>蔬菜罐头 (吨)
+野菜缶詰
+Canned vegetables</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -4937,9 +5268,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>酒类及饮料</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>酒类及饮料
+酒類・飲料
+Liquor &amp; beverages</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -4950,9 +5283,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>果蔬汁 (万吨)</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>果蔬汁 (万吨)
+果汁・野菜汁
+Fruit &amp; vegetable juice</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
@@ -4966,9 +5301,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>啤酒 (万升)</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>啤酒 (万升)
+ビール
+Beer</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
@@ -4982,9 +5319,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>烟草及其制品 (吨)</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>烟草及其制品 (吨)
+たばこ・製品
+Tobacco &amp; products</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -4998,9 +5337,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>烤烟 (吨)</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>烤烟 (吨)
+葉たばこ
+Flue-cured tobacco</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
@@ -5014,9 +5355,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>卷烟 (万条)</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>卷烟 (万条)
+紙巻たばこ
+Cigarettes</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -5030,9 +5373,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>制盐 (吨)</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>制盐 (吨)
+製塩
+Salt production</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
@@ -5046,9 +5391,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>水泥及水泥熟料 (万吨)</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>水泥及水泥熟料 (万吨)
+セメント・クリンカー
+Cement &amp; clinker</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
@@ -5062,9 +5409,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>钨品 (吨)</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>钨品 (吨)
+タングステン製品
+Tungsten products</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
@@ -5078,9 +5427,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>煤及褐煤 (万吨)</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>煤及褐煤 (万吨)
+石炭・褐炭
+Coal &amp; lignite</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
@@ -5094,9 +5445,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>焦炭及半焦炭 (万吨)</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>焦炭及半焦炭 (万吨)
+コークス
+Coke &amp; semi-coke</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
@@ -5110,9 +5463,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>成品油 (万吨)</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>成品油 (万吨)
+石油製品
+Refined oil</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
@@ -5126,9 +5481,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>汽油 (万吨)</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>汽油 (万吨)
+ガソリン
+Gasoline</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
@@ -5142,9 +5499,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>航空煤油 (万吨)</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>航空煤油 (万吨)
+ジェット燃料
+Jet fuel</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -5158,9 +5517,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>柴油 (万吨)</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>柴油 (万吨)
+軽油
+Diesel</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
@@ -5174,9 +5535,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>氧化铝 (万吨)</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>氧化铝 (万吨)
+アルミナ
+Alumina</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
@@ -5190,9 +5553,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>稀土及其制品 (吨)</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>稀土及其制品 (吨)
+レアアース・製品
+Rare earths &amp; products</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
@@ -5206,9 +5571,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>稀土 (吨)</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>稀土 (吨)
+レアアース
+Rare earths</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
@@ -5222,9 +5589,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>基本有机化学品</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>基本有机化学品
+基礎有機化学品
+Basic organic chemicals</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
@@ -5235,9 +5604,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>柠檬酸 (万吨)</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>柠檬酸 (万吨)
+クエン酸
+Citric acid</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
@@ -5251,9 +5622,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>医药材及药品 (吨)</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>医药材及药品 (吨)
+医薬品・原料
+Pharmaceuticals &amp; materials</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
@@ -5267,9 +5640,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>中药材 (吨)</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>中药材 (吨)
+生薬
+Chinese medicinal herbs</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
@@ -5283,9 +5658,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>中式成药 (吨)</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>中式成药 (吨)
+中成薬
+Chinese patent medicine</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
@@ -5299,9 +5676,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>人用疫苗 (千克)</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>人用疫苗 (千克)
+ヒト用ワクチン
+Human vaccines</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
@@ -5315,9 +5694,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>抗菌素(制剂除外) (吨)</t>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>抗菌素(制剂除外) (吨)
+抗生物質(製剤除く)
+Antibiotics (excl. formulations)</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
@@ -5331,9 +5712,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>医用敷料 (吨)</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>医用敷料 (吨)
+医療用ドレッシング
+Medical dressings</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
@@ -5347,9 +5730,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>肥料 (万吨)</t>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>肥料 (万吨)
+肥料
+Fertilizers</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
@@ -5363,9 +5748,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>尿素 (万吨)</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>尿素 (万吨)
+尿素
+Urea</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
@@ -5379,9 +5766,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>硫酸铵 (万吨)</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>硫酸铵 (万吨)
+硫酸アンモニウム
+Ammonium sulfate</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
@@ -5395,9 +5784,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>磷酸氢二铵 (万吨)</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>磷酸氢二铵 (万吨)
+リン酸水素二アンモニウム
+Diammonium phosphate</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
@@ -5411,9 +5802,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>磷酸二氢铵 (万吨)</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>磷酸二氢铵 (万吨)
+リン酸二水素アンモニウム
+Monoammonium phosphate</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
@@ -5427,9 +5820,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>合成有机染料 (吨)</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>合成有机染料 (吨)
+合成有機染料
+Synthetic organic dyes</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
@@ -5443,9 +5838,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>美容化妆品及洗护用品(吨)</t>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>美容化妆品及洗护用品 (吨)
+化粧品・洗浄用品
+Cosmetics &amp; toiletries</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
@@ -5459,9 +5856,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>烟花、爆竹 (吨)</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>烟花、爆竹 (吨)
+花火・爆竹
+Fireworks &amp; firecrackers</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
@@ -5475,9 +5874,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>塑料制品</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>塑料制品
+プラスチック製品
+Plastic products</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -5488,9 +5889,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>橡胶轮胎 (万吨)</t>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>橡胶轮胎 (万吨)
+ゴムタイヤ
+Rubber tyres</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
@@ -5504,9 +5907,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>新的充气橡胶轮胎(万吨)</t>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>新的充气橡胶轮胎 (万吨)
+新品空気入りタイヤ
+New pneumatic tyres</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
@@ -5520,9 +5925,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>皮革、毛皮及其制品</t>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>皮革、毛皮及其制品
+皮革・毛皮・製品
+Leather, fur &amp; products</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
@@ -5533,9 +5940,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>裘皮服装 (吨)</t>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>裘皮服装 (吨)
+毛皮衣類
+Fur clothing</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
@@ -5549,9 +5958,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>箱包及类似容器 (万吨)</t>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>箱包及类似容器 (万吨)
+かばん類
+Bags &amp; similar containers</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
@@ -5565,9 +5976,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>皮革箱包及类似容器 (吨)</t>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>皮革箱包及类似容器 (吨)
+革製かばん類
+Leather bags &amp; containers</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
@@ -5581,9 +5994,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>木及其制品 (万吨)</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>木及其制品 (万吨)
+木材・製品
+Wood &amp; products</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
@@ -5597,9 +6012,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>家用或装饰用木制品(万吨)</t>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>家用或装饰用木制品 (万吨)
+家庭用・装飾用木製品
+Household/decorative wood products</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
@@ -5613,9 +6030,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>胶合板及类似多层板(万立方米)</t>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>胶合板及类似多层板 (万立方米)
+合板
+Plywood</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
@@ -5629,9 +6048,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>植物材料编结品 (吨)</t>
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>植物材料编结品 (吨)
+植物性組物
+Plaited vegetable materials</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
@@ -5645,9 +6066,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>纸浆、纸及其制品 (万吨)</t>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>纸浆、纸及其制品 (万吨)
+パルプ・紙・製品
+Pulp, paper &amp; products</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
@@ -5661,9 +6084,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>纺织原料 (万吨)</t>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>纺织原料 (万吨)
+紡織原料
+Textile raw materials</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
@@ -5677,9 +6102,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>化学纤维纺织原料 (万吨)</t>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>化学纤维纺织原料 (万吨)
+化学繊維原料
+Chemical fiber textile materials</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
@@ -5693,9 +6120,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>纺织纱线、织物及其制品</t>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>纺织纱线、织物及其制品
+紡織糸・織物・製品
+Textile yarn, fabrics &amp; products</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -5706,9 +6135,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>纺织纱线</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>纺织纱线
+紡織糸
+Textile yarn</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
@@ -5719,9 +6150,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>纺织织物</t>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>纺织织物
+織物
+Textile fabrics</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -5732,9 +6165,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>纺织制品</t>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>纺织制品
+紡織製品
+Textile products</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -5745,9 +6180,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>服装及衣着附件</t>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>服装及衣着附件
+衣類・付属品
+Apparel &amp; accessories</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -5758,9 +6195,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>服装</t>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>服装
+衣類
+Apparel</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
@@ -5771,9 +6210,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>鞋靴 (万吨)</t>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>鞋靴 (万吨)
+履物
+Footwear</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
@@ -5787,9 +6228,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>帽类 (万个)</t>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>帽类 (万个)
+帽子
+Hats</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
@@ -5803,9 +6246,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>伞 (万吨)</t>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>伞 (万吨)
+傘
+Umbrellas</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
@@ -5819,9 +6264,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>花岗岩石材及其制品 (万吨)</t>
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>花岗岩石材及其制品 (万吨)
+花崗岩・製品
+Granite &amp; products</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
@@ -5835,9 +6282,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>陶瓷产品 (万吨)</t>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>陶瓷产品 (万吨)
+陶磁器製品
+Ceramic products</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
@@ -5851,9 +6300,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>日用陶瓷 (万吨)</t>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>日用陶瓷 (万吨)
+日用陶磁器
+Household ceramics</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
@@ -5867,9 +6318,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>建筑用陶瓷 (万吨)</t>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>建筑用陶瓷 (万吨)
+建築用陶磁器
+Building ceramics</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
@@ -5883,9 +6336,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>玻璃及其制品</t>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>玻璃及其制品
+ガラス・製品
+Glass &amp; products</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -5896,9 +6351,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>珍珠、宝石及半宝石</t>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>珍珠、宝石及半宝石
+真珠・宝石
+Pearls, gems &amp; semi-precious stones</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -5909,9 +6366,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>贵金属或包贵金属的首饰(吨)</t>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>贵金属或包贵金属的首饰 (吨)
+貴金属・貴金属張り装身具
+Precious-metal jewelry</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
@@ -5925,9 +6384,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>铁合金 (万吨)</t>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>铁合金 (万吨)
+フェロアロイ
+Ferroalloys</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
@@ -5941,9 +6402,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>钢材 (万吨)</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>钢材 (万吨)
+鋼材
+Steel products</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
@@ -5957,9 +6420,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>钢铁棒材 (万吨)</t>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>钢铁棒材 (万吨)
+鋼棒
+Steel bars</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
@@ -5973,9 +6438,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>角钢及型钢 (万吨)</t>
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>角钢及型钢 (万吨)
+形鋼
+Angles &amp; sections</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
@@ -5989,9 +6456,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>钢铁板材 (万吨)</t>
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>钢铁板材 (万吨)
+鋼板
+Steel plates</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
@@ -6005,9 +6474,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>钢铁线材 (万吨)</t>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>钢铁线材 (万吨)
+線材
+Steel wire rod</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
@@ -6021,9 +6492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>未锻轧铜及铜材 (吨)</t>
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>未锻轧铜及铜材 (吨)
+未加工銅・銅材
+Unwrought copper &amp; products</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
@@ -6037,9 +6510,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>未锻轧铝及铝材 (吨)</t>
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>未锻轧铝及铝材 (吨)
+未加工アルミ・アルミ材
+Unwrought aluminum &amp; products</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
@@ -6053,9 +6528,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>家具及其零件</t>
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>家具及其零件
+家具・部品
+Furniture &amp; parts</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
@@ -6066,9 +6543,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>玩具</t>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>玩具
+玩具
+Toys</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
@@ -6079,9 +6558,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>体育用品及设备</t>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>体育用品及设备
+スポーツ用品
+Sports goods &amp; equipment</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -6092,9 +6573,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>笔及其零件</t>
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>笔及其零件
+ペン・部品
+Pens &amp; parts</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -6105,9 +6588,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>机电产品</t>
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>机电产品
+機電製品
+Mechanical &amp; electrical products</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -6118,9 +6603,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>机械基础件</t>
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>机械基础件
+機械基礎部品
+Basic mechanical parts</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
@@ -6131,9 +6618,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>紧固件 (吨)</t>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>紧固件 (吨)
+締結部品
+Fasteners</t>
         </is>
       </c>
       <c r="B96" s="8" t="n">
@@ -6147,9 +6636,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>轴承 (吨)</t>
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>轴承 (吨)
+軸受(ベアリング)
+Bearings</t>
         </is>
       </c>
       <c r="B97" s="8" t="n">
@@ -6163,9 +6654,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>手用或机用工具 (万吨)</t>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>手用或机用工具 (万吨)
+手工具・機械工具
+Hand or machine tools</t>
         </is>
       </c>
       <c r="B98" s="8" t="n">
@@ -6179,9 +6672,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>农业机械</t>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>农业机械
+農業機械
+Agricultural machinery</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
@@ -6192,9 +6687,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>拖拉机 (辆)</t>
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>拖拉机 (辆)
+トラクター
+Tractors</t>
         </is>
       </c>
       <c r="B100" s="8" t="n">
@@ -6208,9 +6705,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>食品加工机械 (万台)</t>
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>食品加工机械 (万台)
+食品加工機械
+Food processing machinery</t>
         </is>
       </c>
       <c r="B101" s="8" t="n">
@@ -6224,9 +6723,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>包装机械 (台)</t>
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>包装机械 (台)
+包装機械
+Packaging machinery</t>
         </is>
       </c>
       <c r="B102" s="8" t="n">
@@ -6240,9 +6741,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>印刷、装订机械及其零件</t>
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>印刷、装订机械及其零件
+印刷・製本機械・部品
+Printing &amp; binding machinery &amp; parts</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
@@ -6253,9 +6756,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>打印机、复印机及一体机 (台)</t>
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>打印机、复印机及一体机 (台)
+プリンタ・複合機
+Printers/copiers</t>
         </is>
       </c>
       <c r="B104" s="8" t="n">
@@ -6269,9 +6774,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>通用机械设备</t>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>通用机械设备
+汎用機械設備
+General machinery</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
@@ -6282,9 +6789,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>泵 (万台)</t>
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>泵 (万台)
+ポンプ
+Pumps</t>
         </is>
       </c>
       <c r="B106" s="8" t="n">
@@ -6298,9 +6807,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>压缩机 (万台)</t>
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>压缩机 (万台)
+圧縮機
+Compressors</t>
         </is>
       </c>
       <c r="B107" s="8" t="n">
@@ -6314,9 +6825,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>分离设备</t>
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>分离设备
+分離設備
+Separation equipment</t>
         </is>
       </c>
       <c r="C108" s="8" t="n">
@@ -6327,9 +6840,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>阀门及类似装置 (万套)</t>
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>阀门及类似装置 (万套)
+バルブ類
+Valves</t>
         </is>
       </c>
       <c r="B109" s="8" t="n">
@@ -6343,9 +6858,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>纺织机械及其零件</t>
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>纺织机械及其零件
+繊維機械・部品
+Textile machinery</t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
@@ -6356,9 +6873,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>缝制机械及其零件</t>
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>缝制机械及其零件
+縫製機械・部品
+Sewing machinery &amp; parts</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
@@ -6369,9 +6888,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>机床 (台)</t>
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>机床 (台)
+工作機械
+Machine tools</t>
         </is>
       </c>
       <c r="B112" s="8" t="n">
@@ -6385,9 +6906,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>自动数据处理设备及其零部件</t>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>自动数据处理设备及其零部件
+自動データ処理装置・部品
+ADP machines &amp; parts</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
@@ -6398,9 +6921,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>自动数据处理设备 (万台)</t>
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>自动数据处理设备 (万台)
+自動データ処理装置
+Automatic data processing machines</t>
         </is>
       </c>
       <c r="B114" s="8" t="n">
@@ -6414,9 +6939,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>平板电脑 (万台)</t>
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>平板电脑 (万台)
+タブレット
+Tablet computers</t>
         </is>
       </c>
       <c r="B115" s="8" t="n">
@@ -6430,9 +6957,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>笔记本电脑 (万台)</t>
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>笔记本电脑 (万台)
+ノートPC
+Laptop computers</t>
         </is>
       </c>
       <c r="B116" s="8" t="n">
@@ -6446,9 +6975,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>中央处理部件 (万台)</t>
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>中央处理部件 (万台)
+CPU
+CPUs</t>
         </is>
       </c>
       <c r="B117" s="8" t="n">
@@ -6462,9 +6993,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>存储部件 (万台)</t>
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>存储部件 (万台)
+記憶装置
+Storage units</t>
         </is>
       </c>
       <c r="B118" s="8" t="n">
@@ -6478,1187 +7011,1304 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>自动数据处理设备的零件、</t>
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>液晶监视器 (万台)
+液晶モニター
+LCD monitors</t>
         </is>
       </c>
       <c r="B119" s="8" t="n">
-        <v>546077</v>
+        <v>10527</v>
       </c>
       <c r="C119" s="8" t="n">
-        <v>22363501</v>
+        <v>9106849</v>
       </c>
       <c r="D119" s="8" t="n">
-        <v>3357923</v>
+        <v>1383651</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>附件 (吨)</t>
-        </is>
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>电工器材
+電気機材
+Electrical materials</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="n">
+        <v>116765926</v>
+      </c>
+      <c r="D120" s="8" t="n">
+        <v>17443795</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>液晶监视器 (万台)</t>
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>变压器 (万个)
+変圧器
+Transformers</t>
         </is>
       </c>
       <c r="B121" s="8" t="n">
-        <v>10527</v>
+        <v>321829</v>
       </c>
       <c r="C121" s="8" t="n">
-        <v>9106849</v>
+        <v>2955229</v>
       </c>
       <c r="D121" s="8" t="n">
-        <v>1383651</v>
+        <v>441900</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>电工器材</t>
-        </is>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>原电池 (亿个)
+一次電池
+Primary cells</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="n">
+        <v>292</v>
       </c>
       <c r="C122" s="8" t="n">
-        <v>116765926</v>
+        <v>1577968</v>
       </c>
       <c r="D122" s="8" t="n">
-        <v>17443795</v>
+        <v>236976</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>变压器 (万个)</t>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>蓄电池 (万个)
+蓄電池
+Storage batteries</t>
         </is>
       </c>
       <c r="B123" s="8" t="n">
-        <v>321829</v>
+        <v>442517</v>
       </c>
       <c r="C123" s="8" t="n">
-        <v>2955229</v>
+        <v>37264706</v>
       </c>
       <c r="D123" s="8" t="n">
-        <v>441900</v>
+        <v>5542712</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>原电池 (亿个)</t>
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>锂离子蓄电池 (万个)
+リチウムイオン電池
+Lithium-ion batteries</t>
         </is>
       </c>
       <c r="B124" s="8" t="n">
-        <v>292</v>
+        <v>376912</v>
       </c>
       <c r="C124" s="8" t="n">
-        <v>1577968</v>
+        <v>34248991</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>236976</v>
+        <v>5089401</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>蓄电池 (万个)</t>
-        </is>
-      </c>
-      <c r="B125" s="8" t="n">
-        <v>442517</v>
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>电气控制装置
+電気制御装置
+Electrical control devices</t>
+        </is>
       </c>
       <c r="C125" s="8" t="n">
-        <v>37264706</v>
+        <v>23862107</v>
       </c>
       <c r="D125" s="8" t="n">
-        <v>5542712</v>
+        <v>3571400</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>锂离子蓄电池 (万个)</t>
-        </is>
-      </c>
-      <c r="B126" s="8" t="n">
-        <v>376912</v>
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>高压开关及控制装置
+高圧開閉・制御装置
+High-voltage switches &amp; controls</t>
+        </is>
       </c>
       <c r="C126" s="8" t="n">
-        <v>34248991</v>
+        <v>1742832</v>
       </c>
       <c r="D126" s="8" t="n">
-        <v>5089401</v>
+        <v>260072</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>电气控制装置</t>
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>低压开关及控制装置
+低圧開閉・制御装置
+Low-voltage switches &amp; controls</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>23862107</v>
+        <v>22119275</v>
       </c>
       <c r="D127" s="8" t="n">
-        <v>3571400</v>
+        <v>3311328</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>高压开关及控制装置</t>
-        </is>
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>电线及电缆 (万吨)
+電線・ケーブル
+Wires &amp; cables</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="n">
+        <v>227</v>
       </c>
       <c r="C128" s="8" t="n">
-        <v>1742832</v>
+        <v>16874812</v>
       </c>
       <c r="D128" s="8" t="n">
-        <v>260072</v>
+        <v>2532733</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>低压开关及控制装置</t>
-        </is>
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>手机 (万台)
+携帯電話
+Mobile phones</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="n">
+        <v>82178</v>
       </c>
       <c r="C129" s="8" t="n">
-        <v>22119275</v>
+        <v>95265999</v>
       </c>
       <c r="D129" s="8" t="n">
-        <v>3311328</v>
+        <v>14265716</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>电线及电缆 (万吨)</t>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>家用电器 (万台)
+家電
+Household appliances</t>
         </is>
       </c>
       <c r="B130" s="8" t="n">
-        <v>227</v>
+        <v>334943</v>
       </c>
       <c r="C130" s="8" t="n">
-        <v>16874812</v>
+        <v>56350333</v>
       </c>
       <c r="D130" s="8" t="n">
-        <v>2532733</v>
+        <v>8481247</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>手机 (万台)</t>
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>电扇 (万台)
+扇風機
+Electric fans</t>
         </is>
       </c>
       <c r="B131" s="8" t="n">
-        <v>82178</v>
+        <v>34706</v>
       </c>
       <c r="C131" s="8" t="n">
-        <v>95265999</v>
+        <v>3708035</v>
       </c>
       <c r="D131" s="8" t="n">
-        <v>14265716</v>
+        <v>562175</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>家用电器 (万台)</t>
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>空调 (万台)
+エアコン
+Air conditioners</t>
         </is>
       </c>
       <c r="B132" s="8" t="n">
-        <v>334943</v>
+        <v>4590</v>
       </c>
       <c r="C132" s="8" t="n">
-        <v>56350333</v>
+        <v>5047837</v>
       </c>
       <c r="D132" s="8" t="n">
-        <v>8481247</v>
+        <v>769706</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>电扇 (万台)</t>
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>冰箱 (万台)
+冷蔵庫
+Refrigerators</t>
         </is>
       </c>
       <c r="B133" s="8" t="n">
-        <v>34706</v>
+        <v>5486</v>
       </c>
       <c r="C133" s="8" t="n">
-        <v>3708035</v>
+        <v>5154685</v>
       </c>
       <c r="D133" s="8" t="n">
-        <v>562175</v>
+        <v>778949</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>空调 (万台)</t>
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>洗衣机 (万台)
+洗濯機
+Washing machines</t>
         </is>
       </c>
       <c r="B134" s="8" t="n">
-        <v>4590</v>
+        <v>2060</v>
       </c>
       <c r="C134" s="8" t="n">
-        <v>5047837</v>
+        <v>1921347</v>
       </c>
       <c r="D134" s="8" t="n">
-        <v>769706</v>
+        <v>287980</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>冰箱 (万台)</t>
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>吸尘器 (万台)
+掃除機
+Vacuum cleaners</t>
         </is>
       </c>
       <c r="B135" s="8" t="n">
-        <v>5486</v>
+        <v>12134</v>
       </c>
       <c r="C135" s="8" t="n">
-        <v>5154685</v>
+        <v>3536151</v>
       </c>
       <c r="D135" s="8" t="n">
-        <v>778949</v>
+        <v>530581</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>洗衣机 (万台)</t>
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>微波炉 (万个)
+電子レンジ
+Microwave ovens</t>
         </is>
       </c>
       <c r="B136" s="8" t="n">
-        <v>2060</v>
+        <v>6051</v>
       </c>
       <c r="C136" s="8" t="n">
-        <v>1921347</v>
+        <v>2273215</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>287980</v>
+        <v>343043</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>吸尘器 (万台)</t>
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>电视机 (万台)
+テレビ
+Televisions</t>
         </is>
       </c>
       <c r="B137" s="8" t="n">
-        <v>12134</v>
+        <v>9290</v>
       </c>
       <c r="C137" s="8" t="n">
-        <v>3536151</v>
+        <v>8467206</v>
       </c>
       <c r="D137" s="8" t="n">
-        <v>530581</v>
+        <v>1272935</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>微波炉 (万个)</t>
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>液晶电视机 (万台)
+液晶テレビ
+LCD TVs</t>
         </is>
       </c>
       <c r="B138" s="8" t="n">
-        <v>6051</v>
+        <v>9218</v>
       </c>
       <c r="C138" s="8" t="n">
-        <v>2273215</v>
+        <v>8275056</v>
       </c>
       <c r="D138" s="8" t="n">
-        <v>343043</v>
+        <v>1244104</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>电视机 (万台)</t>
-        </is>
-      </c>
-      <c r="B139" s="8" t="n">
-        <v>9290</v>
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>音视频设备及其零件
+音響・映像機器・部品
+Audio-video equipment &amp; parts</t>
+        </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>8467206</v>
+        <v>25081434</v>
       </c>
       <c r="D139" s="8" t="n">
-        <v>1272935</v>
+        <v>3759087</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>液晶电视机 (万台)</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="n">
-        <v>9218</v>
-      </c>
-      <c r="C140" s="8" t="n">
-        <v>8275056</v>
-      </c>
-      <c r="D140" s="8" t="n">
-        <v>1244104</v>
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>视频摄录一体机 (万台)
+ビデオカメラ一体型
+Video camcorders</t>
+        </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>音视频设备及其零件</t>
-        </is>
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>数字照相机 (万台)
+デジタルカメラ
+Digital cameras</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="n">
+        <v>1154</v>
       </c>
       <c r="C141" s="8" t="n">
-        <v>25081434</v>
+        <v>707257</v>
       </c>
       <c r="D141" s="8" t="n">
-        <v>3759087</v>
+        <v>105631</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>电视摄像机，数字照相机及</t>
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>无线电广播接收设备 (万台)
+ラジオ受信機
+Radio broadcast receivers</t>
         </is>
       </c>
       <c r="B142" s="8" t="n">
-        <v>42009</v>
+        <v>19797</v>
       </c>
       <c r="C142" s="8" t="n">
-        <v>7030846</v>
+        <v>2196660</v>
       </c>
       <c r="D142" s="8" t="n">
-        <v>1053280</v>
+        <v>328578</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>视频摄录一体机 (万台)</t>
-        </is>
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>音视频设备的零件
+音響・映像機器部品
+Audio-video equipment parts</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="n">
+        <v>7519726</v>
+      </c>
+      <c r="D143" s="8" t="n">
+        <v>1126192</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>数字照相机 (万台)</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="n">
-        <v>1154</v>
-      </c>
-      <c r="C144" s="8" t="n">
-        <v>707257</v>
-      </c>
-      <c r="D144" s="8" t="n">
-        <v>105631</v>
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>有机发光二极管显示屏 (万块)
+有機ELディスプレイ
+OLED display panels</t>
+        </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>无线电广播接收设备 (万台)</t>
-        </is>
-      </c>
-      <c r="B145" s="8" t="n">
-        <v>19797</v>
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>电子元件
+電子部品
+Electronic components</t>
+        </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>2196660</v>
+        <v>187792225</v>
       </c>
       <c r="D145" s="8" t="n">
-        <v>328578</v>
+        <v>28181474</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>音视频设备的零件</t>
-        </is>
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>印刷电路 (亿块)
+プリント基板
+Printed circuits</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="n">
+        <v>433</v>
       </c>
       <c r="C146" s="8" t="n">
-        <v>7519726</v>
+        <v>13102850</v>
       </c>
       <c r="D146" s="8" t="n">
-        <v>1126192</v>
+        <v>1969706</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>有机发光二极管显示屏(万块)</t>
-        </is>
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>二极管及类似半导体器件 (亿个)
+ダイオード等半導体素子
+Diodes &amp; semiconductor devices</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n">
+        <v>6545</v>
+      </c>
+      <c r="C147" s="8" t="n">
+        <v>42725533</v>
+      </c>
+      <c r="D147" s="8" t="n">
+        <v>6416686</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>电子元件</t>
-        </is>
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>太阳能电池 (万个)
+太陽電池
+Solar cells</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="n">
+        <v>407091</v>
       </c>
       <c r="C148" s="8" t="n">
-        <v>187792225</v>
+        <v>30829105</v>
       </c>
       <c r="D148" s="8" t="n">
-        <v>28181474</v>
+        <v>4634405</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>印刷电路 (亿块)</t>
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>集成电路 (亿个)
+集積回路(IC)
+Integrated circuits</t>
         </is>
       </c>
       <c r="B149" s="8" t="n">
-        <v>433</v>
+        <v>2731</v>
       </c>
       <c r="C149" s="8" t="n">
-        <v>13102850</v>
+        <v>101726551</v>
       </c>
       <c r="D149" s="8" t="n">
-        <v>1969706</v>
+        <v>15273828</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>二极管及类似半导体器件(亿个)</t>
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>集装箱 (万个)
+コンテナ
+Containers</t>
         </is>
       </c>
       <c r="B150" s="8" t="n">
-        <v>6545</v>
+        <v>321</v>
       </c>
       <c r="C150" s="8" t="n">
-        <v>42725533</v>
+        <v>9662477</v>
       </c>
       <c r="D150" s="8" t="n">
-        <v>6416686</v>
+        <v>1467107</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>太阳能电池 (万个)</t>
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>摩托车 (万辆)
+オートバイ
+Motorcycles</t>
         </is>
       </c>
       <c r="B151" s="8" t="n">
-        <v>407091</v>
+        <v>2641</v>
       </c>
       <c r="C151" s="8" t="n">
-        <v>30829105</v>
+        <v>7927295</v>
       </c>
       <c r="D151" s="8" t="n">
-        <v>4634405</v>
+        <v>1192735</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>集成电路 (亿个)</t>
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>内燃机摩托车 (万辆)
+エンジン付オートバイ
+Combustion-engine motorcycles</t>
         </is>
       </c>
       <c r="B152" s="8" t="n">
-        <v>2731</v>
+        <v>1012</v>
       </c>
       <c r="C152" s="8" t="n">
-        <v>101726551</v>
+        <v>4362208</v>
       </c>
       <c r="D152" s="8" t="n">
-        <v>15273828</v>
+        <v>657163</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>集装箱 (万个)</t>
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>电动摩托车及脚踏车 (万辆)
+電動バイク・自転車
+Electric motorcycles &amp; bicycles</t>
         </is>
       </c>
       <c r="B153" s="8" t="n">
-        <v>321</v>
+        <v>1612</v>
       </c>
       <c r="C153" s="8" t="n">
-        <v>9662477</v>
+        <v>3540931</v>
       </c>
       <c r="D153" s="8" t="n">
-        <v>1467107</v>
+        <v>531987</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>摩托车 (万辆)</t>
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>自行车 (万辆)
+自転車
+Bicycles</t>
         </is>
       </c>
       <c r="B154" s="8" t="n">
-        <v>2641</v>
+        <v>4128</v>
       </c>
       <c r="C154" s="8" t="n">
-        <v>7927295</v>
+        <v>2408512</v>
       </c>
       <c r="D154" s="8" t="n">
-        <v>1192735</v>
+        <v>363410</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>内燃机摩托车 (万辆)</t>
-        </is>
-      </c>
-      <c r="B155" s="8" t="n">
-        <v>1012</v>
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>摩托车及自行车的零配件
+オートバイ・自転車部品
+Motorcycle &amp; bicycle parts</t>
+        </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>4362208</v>
+        <v>8708700</v>
       </c>
       <c r="D155" s="8" t="n">
-        <v>657163</v>
+        <v>1305755</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>电动摩托车及脚踏车 (万辆)</t>
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>汽车(包含底盘) (万辆)
+自動車(シャシー含む)
+Automobiles (incl. chassis)</t>
         </is>
       </c>
       <c r="B156" s="8" t="n">
-        <v>1612</v>
+        <v>332</v>
       </c>
       <c r="C156" s="8" t="n">
-        <v>3540931</v>
+        <v>40523967</v>
       </c>
       <c r="D156" s="8" t="n">
-        <v>531987</v>
+        <v>6012536</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>自行车 (万辆)</t>
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>乘用车 (辆)
+乗用車
+Passenger cars</t>
         </is>
       </c>
       <c r="B157" s="8" t="n">
-        <v>4128</v>
+        <v>2668260</v>
       </c>
       <c r="C157" s="8" t="n">
-        <v>2408512</v>
+        <v>28648530</v>
       </c>
       <c r="D157" s="8" t="n">
-        <v>363410</v>
+        <v>4242845</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>摩托车及自行车的零配件</t>
-        </is>
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>商用车 (辆)
+商用車
+Commercial vehicles</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="n">
+        <v>648855</v>
       </c>
       <c r="C158" s="8" t="n">
-        <v>8708700</v>
+        <v>11875437</v>
       </c>
       <c r="D158" s="8" t="n">
-        <v>1305755</v>
+        <v>1769691</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>汽车(包含底盘) (万辆)</t>
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>客车(十座及以上) (辆)
+バス(10席以上)
+Buses (10+ seats)</t>
         </is>
       </c>
       <c r="B159" s="8" t="n">
-        <v>332</v>
+        <v>48316</v>
       </c>
       <c r="C159" s="8" t="n">
-        <v>40523967</v>
+        <v>1762448</v>
       </c>
       <c r="D159" s="8" t="n">
-        <v>6012536</v>
+        <v>261482</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>乘用车 (辆)</t>
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>货车 (辆)
+貨物自動車
+Trucks</t>
         </is>
       </c>
       <c r="B160" s="8" t="n">
-        <v>2668260</v>
+        <v>491488</v>
       </c>
       <c r="C160" s="8" t="n">
-        <v>28648530</v>
+        <v>5831840</v>
       </c>
       <c r="D160" s="8" t="n">
-        <v>4242845</v>
+        <v>870041</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>商用车 (辆)</t>
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>专用汽车 (辆)
+特殊用途車
+Special-purpose vehicles</t>
         </is>
       </c>
       <c r="B161" s="8" t="n">
-        <v>648855</v>
+        <v>23915</v>
       </c>
       <c r="C161" s="8" t="n">
-        <v>11875437</v>
+        <v>1354873</v>
       </c>
       <c r="D161" s="8" t="n">
-        <v>1769691</v>
+        <v>201930</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>客车(十座及以上) (辆)</t>
-        </is>
-      </c>
-      <c r="B162" s="8" t="n">
-        <v>48316</v>
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>汽车零配件
+自動車部品
+Auto parts</t>
+        </is>
       </c>
       <c r="C162" s="8" t="n">
-        <v>1762448</v>
+        <v>53797089</v>
       </c>
       <c r="D162" s="8" t="n">
-        <v>261482</v>
+        <v>8062422</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>货车 (辆)</t>
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>车用发动机 (万台)
+車用エンジン
+Vehicle engines</t>
         </is>
       </c>
       <c r="B163" s="8" t="n">
-        <v>491488</v>
+        <v>296</v>
       </c>
       <c r="C163" s="8" t="n">
-        <v>5831840</v>
+        <v>1411954</v>
       </c>
       <c r="D163" s="8" t="n">
-        <v>870041</v>
+        <v>211720</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>专用汽车 (辆)</t>
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>汽车轮胎 (吨)
+自動車用タイヤ
+Automobile tyres</t>
         </is>
       </c>
       <c r="B164" s="8" t="n">
-        <v>23915</v>
+        <v>6510823</v>
       </c>
       <c r="C164" s="8" t="n">
-        <v>1354873</v>
+        <v>10762033</v>
       </c>
       <c r="D164" s="8" t="n">
-        <v>201930</v>
+        <v>1616204</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>汽车零配件</t>
-        </is>
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>婴孩车及其零件 (吨)
+ベビーカー・部品
+Baby carriages &amp; parts</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="n">
+        <v>221432</v>
       </c>
       <c r="C165" s="8" t="n">
-        <v>53797089</v>
+        <v>1103154</v>
       </c>
       <c r="D165" s="8" t="n">
-        <v>8062422</v>
+        <v>165696</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>车用发动机 (万台)</t>
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>船舶 (艘)
+船舶
+Ships</t>
         </is>
       </c>
       <c r="B166" s="8" t="n">
-        <v>296</v>
+        <v>4015</v>
       </c>
       <c r="C166" s="8" t="n">
-        <v>1411954</v>
+        <v>14358967</v>
       </c>
       <c r="D166" s="8" t="n">
-        <v>211720</v>
+        <v>2145145</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>汽车轮胎 (吨)</t>
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>液货船 (艘)
+タンカー
+Tankers</t>
         </is>
       </c>
       <c r="B167" s="8" t="n">
-        <v>6510823</v>
+        <v>136</v>
       </c>
       <c r="C167" s="8" t="n">
-        <v>10762033</v>
+        <v>3504534</v>
       </c>
       <c r="D167" s="8" t="n">
-        <v>1616204</v>
+        <v>521580</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>婴孩车及其零件 (吨)</t>
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>集装箱船 (艘)
+コンテナ船
+Container ships</t>
         </is>
       </c>
       <c r="B168" s="8" t="n">
-        <v>221432</v>
+        <v>114</v>
       </c>
       <c r="C168" s="8" t="n">
-        <v>1103154</v>
+        <v>2993841</v>
       </c>
       <c r="D168" s="8" t="n">
-        <v>165696</v>
+        <v>444930</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>船舶 (艘)</t>
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>散货船 (艘)
+バラ積み船
+Bulk carriers</t>
         </is>
       </c>
       <c r="B169" s="8" t="n">
-        <v>4015</v>
+        <v>295</v>
       </c>
       <c r="C169" s="8" t="n">
-        <v>14358967</v>
+        <v>3874221</v>
       </c>
       <c r="D169" s="8" t="n">
-        <v>2145145</v>
+        <v>583048</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>液货船 (艘)</t>
-        </is>
-      </c>
-      <c r="B170" s="8" t="n">
-        <v>136</v>
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>眼镜及其零件
+眼鏡・部品
+Spectacles &amp; parts</t>
+        </is>
       </c>
       <c r="C170" s="8" t="n">
-        <v>3504534</v>
+        <v>4918392</v>
       </c>
       <c r="D170" s="8" t="n">
-        <v>521580</v>
+        <v>737198</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>集装箱船 (艘)</t>
-        </is>
-      </c>
-      <c r="B171" s="8" t="n">
-        <v>114</v>
-      </c>
-      <c r="C171" s="8" t="n">
-        <v>2993841</v>
-      </c>
-      <c r="D171" s="8" t="n">
-        <v>444930</v>
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>液晶显示板 (万个)
+液晶パネル
+LCD panels</t>
+        </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>散货船 (艘)</t>
-        </is>
-      </c>
-      <c r="B172" s="8" t="n">
-        <v>295</v>
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>计量检测分析自控仪器及器具
+計測・分析・制御機器
+Metrology/analysis/control instruments</t>
+        </is>
       </c>
       <c r="C172" s="8" t="n">
-        <v>3874221</v>
+        <v>19376545</v>
       </c>
       <c r="D172" s="8" t="n">
-        <v>583048</v>
+        <v>2895863</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>眼镜及其零件</t>
-        </is>
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>分析仪器 (台)
+分析機器
+Analytical instruments</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="n">
+        <v>90247760</v>
       </c>
       <c r="C173" s="8" t="n">
-        <v>4918392</v>
+        <v>1632705</v>
       </c>
       <c r="D173" s="8" t="n">
-        <v>737198</v>
+        <v>243911</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>液晶显示板 (万个)</t>
-        </is>
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>医疗仪器及器械
+医療機器
+Medical instruments</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="n">
+        <v>12676995</v>
+      </c>
+      <c r="D174" s="8" t="n">
+        <v>1900637</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>计量检测分析自控仪器及器具</t>
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>钟表及其零件
+時計・部品
+Clocks/watches &amp; parts</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>19376545</v>
+        <v>3181730</v>
       </c>
       <c r="D175" s="8" t="n">
-        <v>2895863</v>
+        <v>476032</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>分析仪器 (台)</t>
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>手表 (万只)
+腕時計
+Watches</t>
         </is>
       </c>
       <c r="B176" s="8" t="n">
-        <v>90247760</v>
+        <v>52371</v>
       </c>
       <c r="C176" s="8" t="n">
-        <v>1632705</v>
+        <v>1309789</v>
       </c>
       <c r="D176" s="8" t="n">
-        <v>243911</v>
+        <v>195798</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>医疗仪器及器械</t>
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>灯具、照明装置及其零件
+照明器具・部品
+Lamps &amp; lighting</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>12676995</v>
+        <v>29939077</v>
       </c>
       <c r="D177" s="8" t="n">
-        <v>1900637</v>
+        <v>4488800</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>钟表及其零件</t>
-        </is>
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>游戏机及其零附件 (吨)
+ゲーム機・部品
+Game consoles &amp; parts</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="n">
+        <v>248466</v>
       </c>
       <c r="C178" s="8" t="n">
-        <v>3181730</v>
+        <v>12680425</v>
       </c>
       <c r="D178" s="8" t="n">
-        <v>476032</v>
+        <v>1883827</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>手表 (万只)</t>
-        </is>
-      </c>
-      <c r="B179" s="8" t="n">
-        <v>52371</v>
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>高新技术产品
+ハイテク製品
+High-tech products</t>
+        </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>1309789</v>
+        <v>630739297</v>
       </c>
       <c r="D179" s="8" t="n">
-        <v>195798</v>
+        <v>94669285</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>灯具、照明装置及其零件</t>
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>生物技术
+バイオ技術
+Biotechnology</t>
         </is>
       </c>
       <c r="C180" s="8" t="n">
-        <v>29939077</v>
+        <v>1427585</v>
       </c>
       <c r="D180" s="8" t="n">
-        <v>4488800</v>
+        <v>216836</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>游戏机及其零附件 (吨)</t>
-        </is>
-      </c>
-      <c r="B181" s="8" t="n">
-        <v>248466</v>
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>生命科学技术
+ライフサイエンス技術
+Life science technology</t>
+        </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>12680425</v>
+        <v>43209338</v>
       </c>
       <c r="D181" s="8" t="n">
-        <v>1883827</v>
+        <v>6529440</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>高新技术产品</t>
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>光电技术
+光電子技術
+Optoelectronic technology</t>
         </is>
       </c>
       <c r="C182" s="8" t="n">
-        <v>630739297</v>
+        <v>24266016</v>
       </c>
       <c r="D182" s="8" t="n">
-        <v>94669285</v>
+        <v>3647753</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>生物技术</t>
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>计算机与通信技术
+コンピュータ・通信技術
+Computer &amp; communication technology</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>1427585</v>
+        <v>353605177</v>
       </c>
       <c r="D183" s="8" t="n">
-        <v>216836</v>
+        <v>53033450</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>生命科学技术</t>
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>电子技术
+電子技術
+Electronic technology</t>
         </is>
       </c>
       <c r="C184" s="8" t="n">
-        <v>43209338</v>
+        <v>172590021</v>
       </c>
       <c r="D184" s="8" t="n">
-        <v>6529440</v>
+        <v>25906852</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>光电技术</t>
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>计算机集成制造技术
+コンピュータ統合生産技術
+CIM technology</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>24266016</v>
+        <v>19283186</v>
       </c>
       <c r="D185" s="8" t="n">
-        <v>3647753</v>
+        <v>2886702</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>计算机与通信技术</t>
-        </is>
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>材料技术 (吨)
+材料技術
+Materials technology</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="n">
+        <v>611305</v>
       </c>
       <c r="C186" s="8" t="n">
-        <v>353605177</v>
+        <v>8905823</v>
       </c>
       <c r="D186" s="8" t="n">
-        <v>53033450</v>
+        <v>1332777</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>电子技术</t>
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>航空航天技术
+航空宇宙技術
+Aerospace technology</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>172590021</v>
+        <v>6651420</v>
       </c>
       <c r="D187" s="8" t="n">
-        <v>25906852</v>
+        <v>995392</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>计算机集成制造技术</t>
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>其他技术
+その他技術
+Other technology</t>
         </is>
       </c>
       <c r="C188" s="8" t="n">
-        <v>19283186</v>
+        <v>800730</v>
       </c>
       <c r="D188" s="8" t="n">
-        <v>2886702</v>
+        <v>120083</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>材料技术 (吨)</t>
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>电动载人汽车 (辆)
+電気乗用車
+Electric passenger vehicles</t>
         </is>
       </c>
       <c r="B189" s="8" t="n">
-        <v>611305</v>
+        <v>1061048</v>
       </c>
       <c r="C189" s="8" t="n">
-        <v>8905823</v>
+        <v>16351821</v>
       </c>
       <c r="D189" s="8" t="n">
-        <v>1332777</v>
+        <v>2412048</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>航空航天技术</t>
-        </is>
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>混合动力客车(10座及以上) (辆)
+ハイブリッドバス(10席以上)
+Hybrid buses (10+ seats)</t>
+        </is>
+      </c>
+      <c r="B190" s="8" t="n">
+        <v>768</v>
       </c>
       <c r="C190" s="8" t="n">
-        <v>6651420</v>
+        <v>71841</v>
       </c>
       <c r="D190" s="8" t="n">
-        <v>995392</v>
+        <v>10505</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>其他技术</t>
-        </is>
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>纯电动客车(10座及以上) (辆)
+BEVバス(10席以上)
+Battery-EV buses (10+ seats)</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="n">
+        <v>6797</v>
       </c>
       <c r="C191" s="8" t="n">
-        <v>800730</v>
+        <v>754820</v>
       </c>
       <c r="D191" s="8" t="n">
-        <v>120083</v>
+        <v>111401</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>电动载人汽车 (辆)</t>
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>非插电式混合动力乘用车 (辆)
+非プラグインHV乗用車
+Non-plug-in hybrid passenger cars</t>
         </is>
       </c>
       <c r="B192" s="8" t="n">
-        <v>1061048</v>
+        <v>17113</v>
       </c>
       <c r="C192" s="8" t="n">
-        <v>16351821</v>
+        <v>197812</v>
       </c>
       <c r="D192" s="8" t="n">
-        <v>2412048</v>
+        <v>28971</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>混合动力客车(10座及以上)(辆)</t>
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>插电式混合动力乘用车 (辆)
+プラグインHV乗用車
+Plug-in hybrid passenger cars</t>
         </is>
       </c>
       <c r="B193" s="8" t="n">
-        <v>768</v>
+        <v>94447</v>
       </c>
       <c r="C193" s="8" t="n">
-        <v>71841</v>
+        <v>1705826</v>
       </c>
       <c r="D193" s="8" t="n">
-        <v>10505</v>
+        <v>252825</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>纯电动客车(10座及以上) (辆)</t>
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>纯电动乘用车 (辆)
+BEV乗用車
+Battery EV passenger cars</t>
         </is>
       </c>
       <c r="B194" s="8" t="n">
-        <v>6797</v>
+        <v>941923</v>
       </c>
       <c r="C194" s="8" t="n">
-        <v>754820</v>
+        <v>13621521</v>
       </c>
       <c r="D194" s="8" t="n">
-        <v>111401</v>
+        <v>2008347</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>非插电式混合动力乘用车 (辆)</t>
-        </is>
-      </c>
-      <c r="B195" s="8" t="n">
-        <v>17113</v>
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>文化产品
+文化製品
+Cultural products</t>
+        </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>197812</v>
+        <v>106808252</v>
       </c>
       <c r="D195" s="8" t="n">
-        <v>28971</v>
+        <v>15965497</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>插电式混合动力乘用车 (辆)</t>
-        </is>
-      </c>
-      <c r="B196" s="8" t="n">
-        <v>94447</v>
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>食品
+食品
+Food</t>
+        </is>
       </c>
       <c r="C196" s="8" t="n">
-        <v>1705826</v>
+        <v>50833837</v>
       </c>
       <c r="D196" s="8" t="n">
-        <v>252825</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>纯电动乘用车 (辆)</t>
-        </is>
-      </c>
-      <c r="B197" s="8" t="n">
-        <v>941923</v>
-      </c>
-      <c r="C197" s="8" t="n">
-        <v>13621521</v>
-      </c>
-      <c r="D197" s="8" t="n">
-        <v>2008347</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>文化产品</t>
-        </is>
-      </c>
-      <c r="C198" s="8" t="n">
-        <v>106808252</v>
-      </c>
-      <c r="D198" s="8" t="n">
-        <v>15965497</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="C199" s="8" t="n">
-        <v>50833837</v>
-      </c>
-      <c r="D199" s="8" t="n">
         <v>7612581</v>
       </c>
     </row>
@@ -7673,7 +8323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7699,7 +8349,9 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>品名 / Item</t>
+          <t>品名
+品目
+Item</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7719,9 +8371,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>农产品</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>农产品
+農産物
+Agricultural products</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -7732,9 +8386,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>肉类(包含杂碎) (万吨)</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>肉类(包含杂碎) (万吨)
+肉類(雑品含む)
+Meat (incl. offal)</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -7748,9 +8404,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>牛肉及牛杂碎 (万吨)</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>牛肉及牛杂碎 (万吨)
+牛肉・牛雑
+Beef &amp; offal</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
@@ -7764,9 +8422,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>牛肉 (万吨)</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>牛肉 (万吨)
+牛肉
+Beef</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -7780,9 +8440,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>猪肉及猪杂碎 (万吨)</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>猪肉及猪杂碎 (万吨)
+豚肉・豚雑
+Pork &amp; offal</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
@@ -7796,9 +8458,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>猪肉 (万吨)</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>猪肉 (万吨)
+豚肉
+Pork</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
@@ -7812,9 +8476,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>羊肉 (吨)</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>羊肉 (吨)
+羊肉
+Mutton</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -7828,9 +8494,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>禽肉 (吨)</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>禽肉 (吨)
+鶏肉
+Poultry meat</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -7844,9 +8512,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>水产品 (万吨)</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>水产品 (万吨)
+水産物
+Aquatic products</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -7860,9 +8530,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>食用水产品 (万吨)</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>食用水产品 (万吨)
+食用水産物
+Edible aquatic products</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -7876,9 +8548,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>冻鱼 (万吨)</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>冻鱼 (万吨)
+冷凍魚
+Frozen fish</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -7892,9 +8566,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>乳品 (万吨)</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>乳品 (万吨)
+乳製品
+Dairy products</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -7908,9 +8584,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>奶粉 (万吨)</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>奶粉 (万吨)
+粉ミルク
+Milk powder</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -7924,9 +8602,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>干鲜瓜果及坚果 (万吨)</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>干鲜瓜果及坚果 (万吨)
+果実・ナッツ
+Fruits &amp; nuts</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
@@ -7940,9 +8620,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>粮食 (万吨)</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>粮食 (万吨)
+食糧
+Grain</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
@@ -7956,9 +8638,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>薯类 (吨)</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>薯类 (吨)
+いも類
+Tubers</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
@@ -7972,9 +8656,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>谷物及谷物粉 (万吨)</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>谷物及谷物粉 (万吨)
+穀物・穀粉
+Cereals &amp; flour</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -7988,9 +8674,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>小麦 (万吨)</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>小麦 (万吨)
+小麦
+Wheat</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
@@ -8004,9 +8692,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>大麦 (万吨)</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>大麦 (万吨)
+大麦
+Barley</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -8020,9 +8710,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>玉米 (万吨)</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>玉米 (万吨)
+とうもろこし
+Maize</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
@@ -8036,9 +8728,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>稻谷及大米 (万吨)</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>稻谷及大米 (万吨)
+もみ・米
+Paddy &amp; rice</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
@@ -8052,9 +8746,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>高粱 (万吨)</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>高粱 (万吨)
+こうりゃん
+Sorghum</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
@@ -8068,9 +8764,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>豆类 (万吨)</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>豆类 (万吨)
+豆類
+Beans</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
@@ -8084,9 +8782,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>大豆 (万吨)</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>大豆 (万吨)
+大豆
+Soybeans</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
@@ -8100,9 +8800,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>食用油 (万吨)</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>食用油 (万吨)
+食用油
+Edible oil</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
@@ -8116,9 +8818,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>食用植物油 (万吨)</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>食用植物油 (万吨)
+食用植物油
+Edible vegetable oil</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
@@ -8132,9 +8836,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>豆油 (万吨)</t>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>豆油 (万吨)
+大豆油
+Soybean oil</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
@@ -8148,9 +8854,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>棕榈油 (万吨)</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>棕榈油 (万吨)
+パーム油
+Palm oil</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
@@ -8164,9 +8872,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>菜子油及芥子油(万吨)</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>菜子油及芥子油 (万吨)
+菜種油・からし油
+Rapeseed/mustard oil</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
@@ -8180,9 +8890,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>食糖 (万吨)</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>食糖 (万吨)
+砂糖
+Sugar</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
@@ -8196,9 +8908,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>酒类及饮料</t>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>酒类及饮料
+酒類・飲料
+Liquor &amp; beverages</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -8209,9 +8923,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>啤酒 (万升)</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>啤酒 (万升)
+ビール
+Beer</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
@@ -8225,9 +8941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>葡萄酒 (万升)</t>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>葡萄酒 (万升)
+ワイン
+Wine</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
@@ -8241,9 +8959,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>制盐 (吨)</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>制盐 (吨)
+製塩
+Salt production</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
@@ -8257,9 +8977,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>金属矿及矿砂 (万吨)</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>金属矿及矿砂 (万吨)
+金属鉱石
+Metal ores</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
@@ -8273,9 +8995,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>铁矿砂及其精矿 (万吨)</t>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>铁矿砂及其精矿 (万吨)
+鉄鉱石
+Iron ore &amp; concentrates</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
@@ -8289,9 +9013,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>铜矿砂及其精矿 (万吨)</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>铜矿砂及其精矿 (万吨)
+銅鉱石
+Copper ore &amp; concentrates</t>
         </is>
       </c>
       <c r="B41" s="8" t="n">
@@ -8305,9 +9031,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>铝矿砂及其精矿 (万吨)</t>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>铝矿砂及其精矿 (万吨)
+アルミ鉱石
+Aluminum ore &amp; concentrates</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
@@ -8321,9 +9049,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>煤及褐煤 (万吨)</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>煤及褐煤 (万吨)
+石炭・褐炭
+Coal &amp; lignite</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
@@ -8337,9 +9067,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>原油 (万吨)</t>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>原油 (万吨)
+原油
+Crude oil</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
@@ -8353,9 +9085,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>成品油 (万吨)</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>成品油 (万吨)
+石油製品
+Refined oil</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
@@ -8369,9 +9103,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>石脑油 (万吨)</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>石脑油 (万吨)
+ナフサ
+Naphtha</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
@@ -8385,9 +9121,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>航空煤油 (万吨)</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>航空煤油 (万吨)
+ジェット燃料
+Jet fuel</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
@@ -8401,9 +9139,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>天然气 (万吨)</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>天然气 (万吨)
+天然ガス
+Natural gas</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
@@ -8417,9 +9157,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>液化天然气 (万吨)</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>液化天然气 (万吨)
+液化天然ガス(LNG)
+LNG</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
@@ -8433,9 +9175,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>气态天然气 (万吨)</t>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>气态天然气 (万吨)
+気体天然ガス
+Gaseous natural gas</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
@@ -8449,9 +9193,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>多晶硅 (吨)</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>多晶硅 (吨)
+多結晶シリコン
+Polysilicon</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
@@ -8465,9 +9211,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>基本有机化学品</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>基本有机化学品
+基礎有機化学品
+Basic organic chemicals</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -8478,9 +9226,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>二甲苯 (万吨)</t>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>二甲苯 (万吨)
+キシレン
+Xylene</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
@@ -8494,9 +9244,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>乙二醇 (万吨)</t>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>乙二醇 (万吨)
+エチレングリコール
+Ethylene glycol</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
@@ -8510,9 +9262,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>医药材及药品 (吨)</t>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>医药材及药品 (吨)
+医薬品・原料
+Pharmaceuticals &amp; materials</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
@@ -8526,9 +9280,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>中药材 (吨)</t>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>中药材 (吨)
+生薬
+Chinese medicinal herbs</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
@@ -8542,9 +9298,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>人用疫苗 (千克)</t>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>人用疫苗 (千克)
+ヒト用ワクチン
+Human vaccines</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
@@ -8558,9 +9316,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>肥料 (万吨)</t>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>肥料 (万吨)
+肥料
+Fertilizers</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
@@ -8574,9 +9334,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>氯化钾 (万吨)</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>氯化钾 (万吨)
+塩化カリウム
+Potassium chloride</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
@@ -8590,9 +9352,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>氮磷钾三元复合肥(万吨)</t>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>氮磷钾三元复合肥 (万吨)
+NPK複合肥料
+NPK compound fertilizer</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
@@ -8606,9 +9370,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>美容化妆品及洗护用品(吨)</t>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>美容化妆品及洗护用品 (吨)
+化粧品・洗浄用品
+Cosmetics &amp; toiletries</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
@@ -8622,9 +9388,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>初级形状的塑料 (万吨)</t>
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>初级形状的塑料 (万吨)
+一次形状プラスチック
+Plastics in primary forms</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
@@ -8638,9 +9406,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>塑料制品</t>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>塑料制品
+プラスチック製品
+Plastic products</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -8651,9 +9421,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>天然及合成橡胶(包括胶乳) (万吨)</t>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>天然及合成橡胶(包括胶乳) (万吨)
+天然・合成ゴム
+Natural &amp; synthetic rubber</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
@@ -8667,9 +9439,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>皮革、毛皮及其制品</t>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>皮革、毛皮及其制品
+皮革・毛皮・製品
+Leather, fur &amp; products</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -8680,9 +9454,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>牛皮革及马皮革 (吨)</t>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>牛皮革及马皮革 (吨)
+牛・馬革
+Bovine &amp; equine leather</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
@@ -8696,9 +9472,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>木及其制品 (万吨)</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>木及其制品 (万吨)
+木材・製品
+Wood &amp; products</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
@@ -8712,9 +9490,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>原木 (万立方米)</t>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>原木 (万立方米)
+原木
+Logs</t>
         </is>
       </c>
       <c r="B68" s="8" t="n">
@@ -8728,9 +9508,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>锯材 (万立方米)</t>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>锯材 (万立方米)
+製材
+Sawnwood</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
@@ -8744,9 +9526,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>纸浆、纸及其制品 (万吨)</t>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>纸浆、纸及其制品 (万吨)
+パルプ・紙・製品
+Pulp, paper &amp; products</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
@@ -8760,9 +9544,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>纸浆 (万吨)</t>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>纸浆 (万吨)
+パルプ
+Pulp</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
@@ -8776,9 +9562,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>纺织原料 (万吨)</t>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>纺织原料 (万吨)
+紡織原料
+Textile raw materials</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
@@ -8792,9 +9580,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>羊毛及毛条 (吨)</t>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>羊毛及毛条 (吨)
+羊毛・トップ
+Wool &amp; tops</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
@@ -8808,9 +9598,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>棉花 (万吨)</t>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>棉花 (万吨)
+綿花
+Cotton</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
@@ -8824,9 +9616,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>纺织纱线、织物及其制品</t>
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>纺织纱线、织物及其制品
+紡織糸・織物・製品
+Textile yarn, fabrics &amp; products</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
@@ -8837,9 +9631,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>纺织纱线</t>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>纺织纱线
+紡織糸
+Textile yarn</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
@@ -8850,9 +9646,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>棉纱线 (万吨)</t>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>棉纱线 (万吨)
+綿糸
+Cotton yarn</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
@@ -8866,9 +9664,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>合成纤维纱线 (吨)</t>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>合成纤维纱线 (吨)
+合成繊維糸
+Synthetic fiber yarn</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
@@ -8882,9 +9682,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>服装及衣着附件</t>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>服装及衣着附件
+衣類・付属品
+Apparel &amp; accessories</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
@@ -8895,9 +9697,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>玻璃及其制品</t>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>玻璃及其制品
+ガラス・製品
+Glass &amp; products</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -8908,9 +9712,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>玻璃纤维及其制品 (吨)</t>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>玻璃纤维及其制品 (吨)
+ガラス繊維・製品
+Glass fiber &amp; products</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
@@ -8924,9 +9730,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>珍珠、宝石及半宝石</t>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>珍珠、宝石及半宝石
+真珠・宝石
+Pearls, gems &amp; semi-precious stones</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -8937,9 +9745,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>钻石 (千克)</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>钻石 (千克)
+ダイヤモンド
+Diamonds</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
@@ -8953,9 +9763,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>钢材 (万吨)</t>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>钢材 (万吨)
+鋼材
+Steel products</t>
         </is>
       </c>
       <c r="B84" s="8" t="n">
@@ -8969,9 +9781,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>未锻轧铜及铜材 (吨)</t>
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>未锻轧铜及铜材 (吨)
+未加工銅・銅材
+Unwrought copper &amp; products</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
@@ -8985,9 +9799,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>未锻轧铝及铝材 (吨)</t>
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>未锻轧铝及铝材 (吨)
+未加工アルミ・アルミ材
+Unwrought aluminum &amp; products</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
@@ -9001,9 +9817,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>机电产品</t>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>机电产品
+機電製品
+Mechanical &amp; electrical products</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -9014,9 +9832,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>机械基础件</t>
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>机械基础件
+機械基礎部品
+Basic mechanical parts</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -9027,9 +9847,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>农业机械</t>
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>农业机械
+農業機械
+Agricultural machinery</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
@@ -9040,9 +9862,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>收获机械 (台)</t>
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>收获机械 (台)
+収穫機械
+Harvesting machinery</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
@@ -9056,9 +9880,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>拖拉机 (辆)</t>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>拖拉机 (辆)
+トラクター
+Tractors</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
@@ -9072,9 +9898,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>食品加工机械 (万台)</t>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>食品加工机械 (万台)
+食品加工機械
+Food processing machinery</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
@@ -9088,9 +9916,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>包装机械 (台)</t>
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>包装机械 (台)
+包装機械
+Packaging machinery</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
@@ -9104,9 +9934,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>印刷、装订机械及其零件</t>
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>印刷、装订机械及其零件
+印刷・製本機械・部品
+Printing &amp; binding machinery &amp; parts</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -9117,9 +9949,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>打印机、复印机及一体机 (台)</t>
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>打印机、复印机及一体机 (台)
+プリンタ・複合機
+Printers/copiers</t>
         </is>
       </c>
       <c r="B95" s="8" t="n">
@@ -9133,9 +9967,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>通用机械设备</t>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>通用机械设备
+汎用機械設備
+General machinery</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
@@ -9146,9 +9982,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>泵 (万台)</t>
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>泵 (万台)
+ポンプ
+Pumps</t>
         </is>
       </c>
       <c r="B97" s="8" t="n">
@@ -9162,9 +10000,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>压缩机 (万台)</t>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>压缩机 (万台)
+圧縮機
+Compressors</t>
         </is>
       </c>
       <c r="B98" s="8" t="n">
@@ -9178,9 +10018,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>分离设备</t>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>分离设备
+分離設備
+Separation equipment</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
@@ -9191,9 +10033,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>阀门及类似装置 (万套)</t>
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>阀门及类似装置 (万套)
+バルブ類
+Valves</t>
         </is>
       </c>
       <c r="B100" s="8" t="n">
@@ -9207,9 +10051,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>机床 (台)</t>
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>机床 (台)
+工作機械
+Machine tools</t>
         </is>
       </c>
       <c r="B101" s="8" t="n">
@@ -9223,9 +10069,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>自动数据处理设备及其零部件</t>
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>自动数据处理设备及其零部件
+自動データ処理装置・部品
+ADP machines &amp; parts</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
@@ -9236,9 +10084,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>自动数据处理设备 (万台)</t>
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>自动数据处理设备 (万台)
+自動データ処理装置
+Automatic data processing machines</t>
         </is>
       </c>
       <c r="B103" s="8" t="n">
@@ -9252,9 +10102,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>中央处理部件 (万台)</t>
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>中央处理部件 (万台)
+CPU
+CPUs</t>
         </is>
       </c>
       <c r="B104" s="8" t="n">
@@ -9268,9 +10120,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>存储部件 (万台)</t>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>存储部件 (万台)
+記憶装置
+Storage units</t>
         </is>
       </c>
       <c r="B105" s="8" t="n">
@@ -9284,9 +10138,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>自动数据处理设备的零件、附件(吨)</t>
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>自动数据处理设备的零件、附件 (吨)
+自動データ処理装置 部品・付属品
+ADP machine parts &amp; accessories</t>
         </is>
       </c>
       <c r="B106" s="8" t="n">
@@ -9300,9 +10156,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>半导体制造设备 (台)</t>
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>半导体制造设备 (台)
+半導体製造装置
+Semiconductor manufacturing equipment</t>
         </is>
       </c>
       <c r="B107" s="8" t="n">
@@ -9316,877 +10174,929 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>制造单晶柱或晶圆用的机器及</t>
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>制造平板显示器用的机器及装置 (台)
+平面ディスプレイ製造装置
+Flat-panel display mfg equipment</t>
         </is>
       </c>
       <c r="B108" s="8" t="n">
-        <v>3262</v>
+        <v>9483</v>
       </c>
       <c r="C108" s="8" t="n">
-        <v>1143861</v>
+        <v>2388877</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>172084</v>
+        <v>361895</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>装置 (台)</t>
-        </is>
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>电工器材
+電気機材
+Electrical materials</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="n">
+        <v>28830529</v>
+      </c>
+      <c r="D109" s="8" t="n">
+        <v>4326427</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>制造半导体器件或集成电路用的机</t>
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>变压器 (万个)
+変圧器
+Transformers</t>
         </is>
       </c>
       <c r="B110" s="8" t="n">
-        <v>15656</v>
+        <v>93137</v>
       </c>
       <c r="C110" s="8" t="n">
-        <v>12425735</v>
+        <v>468409</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>1870476</v>
+        <v>70356</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>器及装置 (台)</t>
-        </is>
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>蓄电池 (万个)
+蓄電池
+Storage batteries</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="n">
+        <v>114780</v>
+      </c>
+      <c r="C111" s="8" t="n">
+        <v>2261504</v>
+      </c>
+      <c r="D111" s="8" t="n">
+        <v>340067</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>制造平板显示器用的机器及装置(台)</t>
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>锂离子蓄电池 (万个)
+リチウムイオン電池
+Lithium-ion batteries</t>
         </is>
       </c>
       <c r="B112" s="8" t="n">
-        <v>9483</v>
+        <v>110862</v>
       </c>
       <c r="C112" s="8" t="n">
-        <v>2388877</v>
+        <v>1984833</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>361895</v>
+        <v>298425</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>电工器材</t>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>电气控制装置
+電気制御装置
+Electrical control devices</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
-        <v>28830529</v>
+        <v>14318054</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>4326427</v>
+        <v>2148532</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>变压器 (万个)</t>
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>电线及电缆 (万吨)
+電線・ケーブル
+Wires &amp; cables</t>
         </is>
       </c>
       <c r="B114" s="8" t="n">
-        <v>93137</v>
+        <v>19</v>
       </c>
       <c r="C114" s="8" t="n">
-        <v>468409</v>
+        <v>3618374</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>70356</v>
+        <v>542260</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>蓄电池 (万个)</t>
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>家用电器 (万台)
+家電
+Household appliances</t>
         </is>
       </c>
       <c r="B115" s="8" t="n">
-        <v>114780</v>
+        <v>2881</v>
       </c>
       <c r="C115" s="8" t="n">
-        <v>2261504</v>
+        <v>1810030</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>340067</v>
+        <v>271948</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>锂离子蓄电池 (万个)</t>
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>电视机 (万台)
+テレビ
+Televisions</t>
         </is>
       </c>
       <c r="B116" s="8" t="n">
-        <v>110862</v>
+        <v>37</v>
       </c>
       <c r="C116" s="8" t="n">
-        <v>1984833</v>
+        <v>134771</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>298425</v>
+        <v>20406</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>电气控制装置</t>
-        </is>
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>液晶电视机 (万台)
+液晶テレビ
+LCD TVs</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="n">
+        <v>37</v>
       </c>
       <c r="C117" s="8" t="n">
-        <v>14318054</v>
+        <v>133180</v>
       </c>
       <c r="D117" s="8" t="n">
-        <v>2148532</v>
+        <v>20167</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>电线及电缆 (万吨)</t>
-        </is>
-      </c>
-      <c r="B118" s="8" t="n">
-        <v>19</v>
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>音视频设备及其零件
+音響・映像機器・部品
+Audio-video equipment &amp; parts</t>
+        </is>
       </c>
       <c r="C118" s="8" t="n">
-        <v>3618374</v>
+        <v>13026846</v>
       </c>
       <c r="D118" s="8" t="n">
-        <v>542260</v>
+        <v>1940129</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>家用电器 (万台)</t>
-        </is>
-      </c>
-      <c r="B119" s="8" t="n">
-        <v>2881</v>
-      </c>
-      <c r="C119" s="8" t="n">
-        <v>1810030</v>
-      </c>
-      <c r="D119" s="8" t="n">
-        <v>271948</v>
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>摄录一体机 (万台)
+ビデオカメラ一体型
+Camcorders</t>
+        </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>电视机 (万台)</t>
-        </is>
-      </c>
-      <c r="B120" s="8" t="n">
-        <v>37</v>
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>音视频设备的零件
+音響・映像機器部品
+Audio-video equipment parts</t>
+        </is>
       </c>
       <c r="C120" s="8" t="n">
-        <v>134771</v>
+        <v>11165443</v>
       </c>
       <c r="D120" s="8" t="n">
-        <v>20406</v>
+        <v>1661617</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>液晶电视机 (万台)</t>
-        </is>
-      </c>
-      <c r="B121" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="C121" s="8" t="n">
-        <v>133180</v>
-      </c>
-      <c r="D121" s="8" t="n">
-        <v>20167</v>
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>有机发光二极管显示屏 (万块)
+有機ELディスプレイ
+OLED display panels</t>
+        </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>音视频设备及其零件</t>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>电子元件
+電子部品
+Electronic components</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
-        <v>13026846</v>
+        <v>316238871</v>
       </c>
       <c r="D122" s="8" t="n">
-        <v>1940129</v>
+        <v>47504899</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>电视摄像机,数字照相机及视频</t>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>电容器 (万吨)
+コンデンサ
+Capacitors</t>
         </is>
       </c>
       <c r="B123" s="8" t="n">
-        <v>3024</v>
+        <v>6</v>
       </c>
       <c r="C123" s="8" t="n">
-        <v>1603276</v>
+        <v>6801772</v>
       </c>
       <c r="D123" s="8" t="n">
-        <v>240206</v>
+        <v>1023964</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>摄录一体机 (万台)</t>
-        </is>
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>印刷电路 (亿块)
+プリント基板
+Printed circuits</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="n">
+        <v>354</v>
+      </c>
+      <c r="C124" s="8" t="n">
+        <v>7133002</v>
+      </c>
+      <c r="D124" s="8" t="n">
+        <v>1071682</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>音视频设备的零件</t>
-        </is>
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>二极管及类似半导体器件 (亿个)
+ダイオード等半導体素子
+Diodes &amp; semiconductor devices</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="n">
+        <v>5960</v>
       </c>
       <c r="C125" s="8" t="n">
-        <v>11165443</v>
+        <v>19325938</v>
       </c>
       <c r="D125" s="8" t="n">
-        <v>1661617</v>
+        <v>2898681</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>有机发光二极管显示屏(万块)</t>
-        </is>
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>集成电路 (亿个)
+集積回路(IC)
+Integrated circuits</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="n">
+        <v>5380</v>
+      </c>
+      <c r="C126" s="8" t="n">
+        <v>275954304</v>
+      </c>
+      <c r="D126" s="8" t="n">
+        <v>41459934</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>电子元件</t>
-        </is>
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>汽车(包含底盘) (万辆)
+自動車(シャシー含む)
+Automobiles (incl. chassis)</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="n">
+        <v>88</v>
       </c>
       <c r="C127" s="8" t="n">
-        <v>316238871</v>
+        <v>35287361</v>
       </c>
       <c r="D127" s="8" t="n">
-        <v>47504899</v>
+        <v>5323375</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>电容器 (万吨)</t>
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>乘用车 (辆)
+乗用車
+Passenger cars</t>
         </is>
       </c>
       <c r="B128" s="8" t="n">
-        <v>6</v>
+        <v>863852</v>
       </c>
       <c r="C128" s="8" t="n">
-        <v>6801772</v>
+        <v>34632134</v>
       </c>
       <c r="D128" s="8" t="n">
-        <v>1023964</v>
+        <v>5225868</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>印刷电路 (亿块)</t>
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>商用车 (辆)
+商用車
+Commercial vehicles</t>
         </is>
       </c>
       <c r="B129" s="8" t="n">
-        <v>354</v>
+        <v>13657</v>
       </c>
       <c r="C129" s="8" t="n">
-        <v>7133002</v>
+        <v>655227</v>
       </c>
       <c r="D129" s="8" t="n">
-        <v>1071682</v>
+        <v>97507</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>二极管及类似半导体器件(亿个)</t>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>货车 (辆)
+貨物自動車
+Trucks</t>
         </is>
       </c>
       <c r="B130" s="8" t="n">
-        <v>5960</v>
+        <v>11512</v>
       </c>
       <c r="C130" s="8" t="n">
-        <v>19325938</v>
+        <v>514013</v>
       </c>
       <c r="D130" s="8" t="n">
-        <v>2898681</v>
+        <v>76193</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>集成电路 (亿个)</t>
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>专用汽车 (辆)
+特殊用途車
+Special-purpose vehicles</t>
         </is>
       </c>
       <c r="B131" s="8" t="n">
-        <v>5380</v>
+        <v>152</v>
       </c>
       <c r="C131" s="8" t="n">
-        <v>275954304</v>
+        <v>54219</v>
       </c>
       <c r="D131" s="8" t="n">
-        <v>41459934</v>
+        <v>8228</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>汽车(包含底盘) (万辆)</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="n">
-        <v>88</v>
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>汽车零配件
+自動車部品
+Auto parts</t>
+        </is>
       </c>
       <c r="C132" s="8" t="n">
-        <v>35287361</v>
+        <v>20740608</v>
       </c>
       <c r="D132" s="8" t="n">
-        <v>5323375</v>
+        <v>3123056</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>乘用车 (辆)</t>
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>车用发动机 (万台)
+車用エンジン
+Vehicle engines</t>
         </is>
       </c>
       <c r="B133" s="8" t="n">
-        <v>863852</v>
+        <v>25</v>
       </c>
       <c r="C133" s="8" t="n">
-        <v>34632134</v>
+        <v>593032</v>
       </c>
       <c r="D133" s="8" t="n">
-        <v>5225868</v>
+        <v>88935</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>商用车 (辆)</t>
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>汽车轮胎 (吨)
+自動車用タイヤ
+Automobile tyres</t>
         </is>
       </c>
       <c r="B134" s="8" t="n">
-        <v>13657</v>
+        <v>96150</v>
       </c>
       <c r="C134" s="8" t="n">
-        <v>655227</v>
+        <v>397434</v>
       </c>
       <c r="D134" s="8" t="n">
-        <v>97507</v>
+        <v>59968</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>货车 (辆)</t>
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>飞机及其他航空器 (架)
+航空機
+Aircraft</t>
         </is>
       </c>
       <c r="B135" s="8" t="n">
-        <v>11512</v>
+        <v>43643</v>
       </c>
       <c r="C135" s="8" t="n">
-        <v>514013</v>
+        <v>5258705</v>
       </c>
       <c r="D135" s="8" t="n">
-        <v>76193</v>
+        <v>775672</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>专用汽车 (辆)</t>
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>空载重量超过2吨的飞机 (架)
+自重2トン超の航空機
+Aircraft over 2 tons</t>
         </is>
       </c>
       <c r="B136" s="8" t="n">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C136" s="8" t="n">
-        <v>54219</v>
+        <v>5182121</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>8228</v>
+        <v>764186</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>汽车零配件</t>
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>航空器零部件
+航空機部品
+Aircraft parts</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>20740608</v>
+        <v>6463980</v>
       </c>
       <c r="D137" s="8" t="n">
-        <v>3123056</v>
+        <v>968735</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>车用发动机 (万台)</t>
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>涡轮喷气发动机 (台)
+ターボジェットエンジン
+Turbojet engines</t>
         </is>
       </c>
       <c r="B138" s="8" t="n">
-        <v>25</v>
+        <v>754</v>
       </c>
       <c r="C138" s="8" t="n">
-        <v>593032</v>
+        <v>2434985</v>
       </c>
       <c r="D138" s="8" t="n">
-        <v>88935</v>
+        <v>365070</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>汽车轮胎 (吨)</t>
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>涡轮螺桨发动机 (台)
+ターボプロップエンジン
+Turboprop engines</t>
         </is>
       </c>
       <c r="B139" s="8" t="n">
-        <v>96150</v>
+        <v>31</v>
       </c>
       <c r="C139" s="8" t="n">
-        <v>397434</v>
+        <v>4089</v>
       </c>
       <c r="D139" s="8" t="n">
-        <v>59968</v>
+        <v>619</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>飞机及其他航空器 (架)</t>
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>船舶 (艘)
+船舶
+Ships</t>
         </is>
       </c>
       <c r="B140" s="8" t="n">
-        <v>43643</v>
+        <v>3434</v>
       </c>
       <c r="C140" s="8" t="n">
-        <v>5258705</v>
+        <v>682008</v>
       </c>
       <c r="D140" s="8" t="n">
-        <v>775672</v>
+        <v>103697</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>空载重量超过2吨的飞机 (架)</t>
-        </is>
-      </c>
-      <c r="B141" s="8" t="n">
-        <v>131</v>
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>计量检测分析自控仪器及器具
+計測・分析・制御機器
+Metrology/analysis/control instruments</t>
+        </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>5182121</v>
+        <v>28855288</v>
       </c>
       <c r="D141" s="8" t="n">
-        <v>764186</v>
+        <v>4322592</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>航空器零部件</t>
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>医疗仪器及器械
+医療機器
+Medical instruments</t>
         </is>
       </c>
       <c r="C142" s="8" t="n">
-        <v>6463980</v>
+        <v>9605971</v>
       </c>
       <c r="D142" s="8" t="n">
-        <v>968735</v>
+        <v>1436910</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>涡轮喷气发动机 (台)</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="n">
-        <v>754</v>
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>钟表及其零件
+時計・部品
+Clocks/watches &amp; parts</t>
+        </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>2434985</v>
+        <v>2846663</v>
       </c>
       <c r="D143" s="8" t="n">
-        <v>365070</v>
+        <v>427183</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>涡轮螺桨发动机 (台)</t>
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>手表 (万只)
+腕時計
+Watches</t>
         </is>
       </c>
       <c r="B144" s="8" t="n">
-        <v>31</v>
+        <v>1327</v>
       </c>
       <c r="C144" s="8" t="n">
-        <v>4089</v>
+        <v>2460675</v>
       </c>
       <c r="D144" s="8" t="n">
-        <v>619</v>
+        <v>369395</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>船舶 (艘)</t>
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>电动手表 (万只)
+電子式腕時計
+Electronic watches</t>
         </is>
       </c>
       <c r="B145" s="8" t="n">
-        <v>3434</v>
+        <v>1165</v>
       </c>
       <c r="C145" s="8" t="n">
-        <v>682008</v>
+        <v>578623</v>
       </c>
       <c r="D145" s="8" t="n">
-        <v>103697</v>
+        <v>86568</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>计量检测分析自控仪器及器具</t>
-        </is>
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>机械手表 (万只)
+機械式腕時計
+Mechanical watches</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="n">
+        <v>162</v>
       </c>
       <c r="C146" s="8" t="n">
-        <v>28855288</v>
+        <v>1882052</v>
       </c>
       <c r="D146" s="8" t="n">
-        <v>4322592</v>
+        <v>282827</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>医疗仪器及器械</t>
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>高新技术产品
+ハイテク製品
+High-tech products</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>9605971</v>
+        <v>506652721</v>
       </c>
       <c r="D147" s="8" t="n">
-        <v>1436910</v>
+        <v>76056873</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>钟表及其零件</t>
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>生物技术
+バイオ技術
+Biotechnology</t>
         </is>
       </c>
       <c r="C148" s="8" t="n">
-        <v>2846663</v>
+        <v>4335785</v>
       </c>
       <c r="D148" s="8" t="n">
-        <v>427183</v>
+        <v>649490</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>手表 (万只)</t>
-        </is>
-      </c>
-      <c r="B149" s="8" t="n">
-        <v>1327</v>
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>生命科学技术
+ライフサイエンス技術
+Life science technology</t>
+        </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>2460675</v>
+        <v>34723126</v>
       </c>
       <c r="D149" s="8" t="n">
-        <v>369395</v>
+        <v>5189007</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>电动手表 (万只)</t>
-        </is>
-      </c>
-      <c r="B150" s="8" t="n">
-        <v>1165</v>
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>光电技术
+光電子技術
+Optoelectronic technology</t>
+        </is>
       </c>
       <c r="C150" s="8" t="n">
-        <v>578623</v>
+        <v>21024512</v>
       </c>
       <c r="D150" s="8" t="n">
-        <v>86568</v>
+        <v>3160745</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>机械手表 (万只)</t>
-        </is>
-      </c>
-      <c r="B151" s="8" t="n">
-        <v>162</v>
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>计算机与通信技术
+コンピュータ・通信技術
+Computer &amp; communication technology</t>
+        </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>1882052</v>
+        <v>72903909</v>
       </c>
       <c r="D151" s="8" t="n">
-        <v>282827</v>
+        <v>10941079</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>高新技术产品</t>
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>电子技术
+電子技術
+Electronic technology</t>
         </is>
       </c>
       <c r="C152" s="8" t="n">
-        <v>506652721</v>
+        <v>313119560</v>
       </c>
       <c r="D152" s="8" t="n">
-        <v>76056873</v>
+        <v>47031162</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>生物技术</t>
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>计算机集成制造技术
+コンピュータ統合生産技術
+CIM technology</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>4335785</v>
+        <v>39958584</v>
       </c>
       <c r="D153" s="8" t="n">
-        <v>649490</v>
+        <v>6011309</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>生命科学技术</t>
-        </is>
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>材料技术 (吨)
+材料技術
+Materials technology</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="n">
+        <v>38122</v>
       </c>
       <c r="C154" s="8" t="n">
-        <v>34723126</v>
+        <v>4685992</v>
       </c>
       <c r="D154" s="8" t="n">
-        <v>5189007</v>
+        <v>704003</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>光电技术</t>
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>航空航天技术
+航空宇宙技術
+Aerospace technology</t>
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>21024512</v>
+        <v>14942848</v>
       </c>
       <c r="D155" s="8" t="n">
-        <v>3160745</v>
+        <v>2226261</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>计算机与通信技术</t>
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>其他技术
+その他技術
+Other technology</t>
         </is>
       </c>
       <c r="C156" s="8" t="n">
-        <v>72903909</v>
+        <v>958405</v>
       </c>
       <c r="D156" s="8" t="n">
-        <v>10941079</v>
+        <v>143818</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>电子技术</t>
-        </is>
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>电动载人汽车 (辆)
+電気乗用車
+Electric passenger vehicles</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="n">
+        <v>132130</v>
       </c>
       <c r="C157" s="8" t="n">
-        <v>313119560</v>
+        <v>5101262</v>
       </c>
       <c r="D157" s="8" t="n">
-        <v>47031162</v>
+        <v>765952</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>计算机集成制造技术</t>
-        </is>
-      </c>
-      <c r="C158" s="8" t="n">
-        <v>39958584</v>
-      </c>
-      <c r="D158" s="8" t="n">
-        <v>6011309</v>
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>混合动力客车(10座及以上) (辆)
+ハイブリッドバス(10席以上)
+Hybrid buses (10+ seats)</t>
+        </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>材料技术 (吨)</t>
-        </is>
-      </c>
-      <c r="B159" s="8" t="n">
-        <v>38122</v>
-      </c>
-      <c r="C159" s="8" t="n">
-        <v>4685992</v>
-      </c>
-      <c r="D159" s="8" t="n">
-        <v>704003</v>
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>纯电动客车(10座及以上) (辆)
+BEVバス(10席以上)
+Battery-EV buses (10+ seats)</t>
+        </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>航空航天技术</t>
-        </is>
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>非插电式混合动力乘用车 (辆)
+非プラグインHV乗用車
+Non-plug-in hybrid passenger cars</t>
+        </is>
+      </c>
+      <c r="B160" s="8" t="n">
+        <v>89323</v>
       </c>
       <c r="C160" s="8" t="n">
-        <v>14942848</v>
+        <v>2717961</v>
       </c>
       <c r="D160" s="8" t="n">
-        <v>2226261</v>
+        <v>409962</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>其他技术</t>
-        </is>
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>插电式混合动力乘用车 (辆)
+プラグインHV乗用車
+Plug-in hybrid passenger cars</t>
+        </is>
+      </c>
+      <c r="B161" s="8" t="n">
+        <v>24618</v>
       </c>
       <c r="C161" s="8" t="n">
-        <v>958405</v>
+        <v>1410592</v>
       </c>
       <c r="D161" s="8" t="n">
-        <v>143818</v>
+        <v>211535</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>电动载人汽车 (辆)</t>
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>纯电动乘用车 (辆)
+BEV乗用車
+Battery EV passenger cars</t>
         </is>
       </c>
       <c r="B162" s="8" t="n">
-        <v>132130</v>
+        <v>18189</v>
       </c>
       <c r="C162" s="8" t="n">
-        <v>5101262</v>
+        <v>972709</v>
       </c>
       <c r="D162" s="8" t="n">
-        <v>765952</v>
+        <v>144456</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>混合动力客车(10座及以上) (辆)</t>
-        </is>
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>文化产品
+文化製品
+Cultural products</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="n">
+        <v>10635474</v>
+      </c>
+      <c r="D163" s="8" t="n">
+        <v>1587436</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>纯电动客车(10座及以上) (辆)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>非插电式混合动力乘用车 (辆)</t>
-        </is>
-      </c>
-      <c r="B165" s="8" t="n">
-        <v>89323</v>
-      </c>
-      <c r="C165" s="8" t="n">
-        <v>2717961</v>
-      </c>
-      <c r="D165" s="8" t="n">
-        <v>409962</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>插电式混合动力乘用车 (辆)</t>
-        </is>
-      </c>
-      <c r="B166" s="8" t="n">
-        <v>24618</v>
-      </c>
-      <c r="C166" s="8" t="n">
-        <v>1410592</v>
-      </c>
-      <c r="D166" s="8" t="n">
-        <v>211535</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>纯电动乘用车 (辆)</t>
-        </is>
-      </c>
-      <c r="B167" s="8" t="n">
-        <v>18189</v>
-      </c>
-      <c r="C167" s="8" t="n">
-        <v>972709</v>
-      </c>
-      <c r="D167" s="8" t="n">
-        <v>144456</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>文化产品</t>
-        </is>
-      </c>
-      <c r="C168" s="8" t="n">
-        <v>10635474</v>
-      </c>
-      <c r="D168" s="8" t="n">
-        <v>1587436</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="C169" s="8" t="n">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>食品
+食品
+Food</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="n">
         <v>138507220</v>
       </c>
-      <c r="D169" s="8" t="n">
+      <c r="D164" s="8" t="n">
         <v>20760179</v>
       </c>
     </row>
